--- a/data/source/weekly/cs-en-us-024pct.xlsx
+++ b/data/source/weekly/cs-en-us-024pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -692,10 +692,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -895,29 +895,29 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="15">
+        <v>2</v>
+      </c>
+      <c r="E15" s="14">
+        <v>-100</v>
       </c>
       <c r="F15" s="15">
         <v>1</v>
       </c>
       <c r="G15" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15" s="14">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="I15" s="15">
         <v>1</v>
       </c>
       <c r="J15" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K15" s="14">
-        <v>-66.666666666666</v>
+        <v>-80</v>
       </c>
       <c r="L15" s="14">
         <v>-66.666666666666</v>
@@ -936,38 +936,38 @@
       <c r="C16" s="15">
         <v>2</v>
       </c>
-      <c r="D16" s="15">
-        <v>1</v>
-      </c>
-      <c r="E16" s="14">
-        <v>100</v>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G16" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H16" s="14">
-        <v>-12.5</v>
+        <v>50</v>
       </c>
       <c r="I16" s="15">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J16" s="15">
         <v>12</v>
       </c>
       <c r="K16" s="14">
-        <v>-8.333333333333</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L16" s="14">
-        <v>-15.384615384615</v>
+        <v>-30</v>
       </c>
       <c r="M16" s="14">
-        <v>-50</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="N16" s="14">
-        <v>-86.25</v>
+        <v>-84.269662921348</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E17" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F17" s="15">
         <v>9</v>
       </c>
       <c r="G17" s="15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H17" s="14">
-        <v>-18.181818181818</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="I17" s="15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J17" s="15">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="K17" s="14">
-        <v>-42.105263157894</v>
+        <v>-48</v>
       </c>
       <c r="L17" s="14">
-        <v>-21.428571428571</v>
+        <v>-18.75</v>
       </c>
       <c r="M17" s="14">
-        <v>-26.666666666666</v>
+        <v>-18.75</v>
       </c>
       <c r="N17" s="14">
-        <v>-73.170731707317</v>
+        <v>-74</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,7 +1016,7 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>20</v>
@@ -1025,31 +1025,31 @@
         <v>21</v>
       </c>
       <c r="F18" s="15">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G18" s="15">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H18" s="14">
-        <v>38.461538461538</v>
+        <v>220</v>
       </c>
       <c r="I18" s="15">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J18" s="15">
         <v>17</v>
       </c>
       <c r="K18" s="14">
-        <v>52.941176470588</v>
+        <v>58.823529411764</v>
       </c>
       <c r="L18" s="14">
-        <v>73.333333333333</v>
+        <v>68.75</v>
       </c>
       <c r="M18" s="14">
-        <v>44.444444444444</v>
+        <v>35</v>
       </c>
       <c r="N18" s="14">
-        <v>-80.597014925373</v>
+        <v>-81.506849315068</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D19" s="15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E19" s="14">
-        <v>-50</v>
+        <v>160</v>
       </c>
       <c r="F19" s="15">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G19" s="15">
         <v>31</v>
       </c>
       <c r="H19" s="14">
-        <v>9.677419354838</v>
+        <v>16.129032258064</v>
       </c>
       <c r="I19" s="15">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="J19" s="15">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="K19" s="14">
-        <v>2.222222222222</v>
+        <v>22</v>
       </c>
       <c r="L19" s="14">
-        <v>9.523809523809</v>
+        <v>24.489795918367</v>
       </c>
       <c r="M19" s="14">
-        <v>-14.814814814814</v>
+        <v>0</v>
       </c>
       <c r="N19" s="14">
-        <v>-54.901960784313</v>
+        <v>-45.045045045045</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,7 +1098,7 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1107,31 +1107,31 @@
         <v>21</v>
       </c>
       <c r="F20" s="15">
-        <v>5</v>
-      </c>
-      <c r="G20" s="15">
-        <v>3</v>
-      </c>
-      <c r="H20" s="14">
-        <v>66.666666666666</v>
+        <v>7</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I20" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J20" s="15">
         <v>3</v>
       </c>
       <c r="K20" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L20" s="14">
-        <v>20</v>
+        <v>28.571428571428</v>
       </c>
       <c r="M20" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N20" s="14">
-        <v>-94.174757281553</v>
+        <v>-91.964285714285</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
+        <v>21</v>
+      </c>
+      <c r="D21" s="17">
         <v>13</v>
       </c>
-      <c r="D21" s="17">
-        <v>11</v>
-      </c>
       <c r="E21" s="18">
-        <v>18.181818181818</v>
+        <v>61.538461538461</v>
       </c>
       <c r="F21" s="17">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G21" s="17">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H21" s="18">
-        <v>7.246376811594</v>
+        <v>32.203389830508</v>
       </c>
       <c r="I21" s="17">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="J21" s="17">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="K21" s="18">
-        <v>2.020202020202</v>
+        <v>11.607142857142</v>
       </c>
       <c r="L21" s="18">
-        <v>9.782608695652</v>
+        <v>12.612612612612</v>
       </c>
       <c r="M21" s="18">
-        <v>-10.619469026548</v>
+        <v>-1.574803149606</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.372591006424</v>
+        <v>-75.728155339805</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="15">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,28 +1189,28 @@
         <v>21</v>
       </c>
       <c r="F22" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G22" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" s="14">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="I22" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J22" s="15">
         <v>3</v>
       </c>
       <c r="K22" s="14">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="L22" s="14">
         <v>0</v>
       </c>
       <c r="M22" s="14">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1224,34 +1224,34 @@
         <v>1</v>
       </c>
       <c r="D23" s="15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E23" s="14">
-        <v>0</v>
+        <v>-80</v>
       </c>
       <c r="F23" s="15">
         <v>5</v>
       </c>
       <c r="G23" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H23" s="14">
-        <v>-58.333333333333</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="I23" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J23" s="15">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K23" s="14">
-        <v>-62.5</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L23" s="14">
-        <v>-40</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="M23" s="14">
-        <v>-40</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D24" s="15">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="E24" s="14">
-        <v>-64.406779661017</v>
+        <v>-19.444444444444</v>
       </c>
       <c r="F24" s="15">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G24" s="15">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="H24" s="14">
-        <v>-38.356164383561</v>
+        <v>-44.720496894409</v>
       </c>
       <c r="I24" s="15">
-        <v>149</v>
+        <v>176</v>
       </c>
       <c r="J24" s="15">
-        <v>178</v>
+        <v>214</v>
       </c>
       <c r="K24" s="14">
-        <v>-16.292134831460</v>
+        <v>-17.757009345794</v>
       </c>
       <c r="L24" s="14">
-        <v>0.675675675675</v>
+        <v>1.734104046242</v>
       </c>
       <c r="M24" s="14">
-        <v>29.565217391304</v>
+        <v>36.434108527131</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D25" s="15">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E25" s="14">
-        <v>-73.684210526315</v>
+        <v>-37.5</v>
       </c>
       <c r="F25" s="15">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G25" s="15">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="H25" s="14">
-        <v>-39.784946236559</v>
+        <v>-48.076923076923</v>
       </c>
       <c r="I25" s="15">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="J25" s="15">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="K25" s="14">
-        <v>-30.172413793103</v>
+        <v>-31.428571428571</v>
       </c>
       <c r="L25" s="14">
-        <v>-13.829787234042</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D26" s="15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E26" s="14">
-        <v>500</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F26" s="15">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G26" s="15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H26" s="14">
-        <v>47.058823529411</v>
+        <v>72.222222222222</v>
       </c>
       <c r="I26" s="15">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="J26" s="15">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K26" s="14">
-        <v>70.833333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L26" s="14">
-        <v>24.242424242424</v>
+        <v>35.135135135135</v>
       </c>
       <c r="M26" s="14">
-        <v>32.258064516129</v>
+        <v>38.888888888888</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,29 +1387,29 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="15">
+        <v>2</v>
+      </c>
+      <c r="E27" s="14">
+        <v>-100</v>
       </c>
       <c r="F27" s="15">
         <v>1</v>
       </c>
       <c r="G27" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" s="14">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="I27" s="15">
         <v>1</v>
       </c>
       <c r="J27" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K27" s="14">
-        <v>-66.666666666666</v>
+        <v>-80</v>
       </c>
       <c r="L27" s="14">
         <v>-66.666666666666</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>2</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F28" s="15">
+        <v>6</v>
+      </c>
+      <c r="G28" s="15">
+        <v>6</v>
+      </c>
+      <c r="H28" s="14">
         <v>0</v>
-      </c>
-      <c r="F28" s="15">
-        <v>8</v>
-      </c>
-      <c r="G28" s="15">
-        <v>5</v>
-      </c>
-      <c r="H28" s="14">
-        <v>60</v>
       </c>
       <c r="I28" s="15">
         <v>8</v>
       </c>
       <c r="J28" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K28" s="14">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="L28" s="14">
-        <v>166.666666666667</v>
+        <v>100</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,32 +1551,32 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="D31" s="15">
+        <v>1</v>
+      </c>
+      <c r="E31" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F31" s="15">
+        <v>2</v>
       </c>
       <c r="G31" s="15">
         <v>1</v>
       </c>
       <c r="H31" s="14">
-        <v>-100</v>
-      </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
+        <v>100</v>
+      </c>
+      <c r="I31" s="15">
+        <v>2</v>
       </c>
       <c r="J31" s="15">
         <v>1</v>
       </c>
       <c r="K31" s="14">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L31" s="14">
-        <v>-100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-024pct.xlsx
+++ b/data/source/weekly/cs-en-us-024pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="15">
+      <c r="C15" s="15">
+        <v>1</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="15">
         <v>2</v>
       </c>
-      <c r="E15" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="15">
-        <v>1</v>
-      </c>
       <c r="G15" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H15" s="14">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="I15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15" s="15">
         <v>5</v>
       </c>
       <c r="K15" s="14">
-        <v>-80</v>
+        <v>-60</v>
       </c>
       <c r="L15" s="14">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="M15" s="13" t="s">
-        <v>21</v>
+        <v>-33.333333333333</v>
+      </c>
+      <c r="M15" s="14">
+        <v>100</v>
       </c>
       <c r="N15" s="14">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>2</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="D16" s="15">
+        <v>4</v>
+      </c>
+      <c r="E16" s="14">
+        <v>-25</v>
       </c>
       <c r="F16" s="15">
         <v>9</v>
       </c>
       <c r="G16" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H16" s="14">
-        <v>50</v>
+        <v>12.5</v>
       </c>
       <c r="I16" s="15">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J16" s="15">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K16" s="14">
-        <v>16.666666666666</v>
+        <v>6.25</v>
       </c>
       <c r="L16" s="14">
-        <v>-30</v>
+        <v>-37.037037037037</v>
       </c>
       <c r="M16" s="14">
-        <v>-46.153846153846</v>
+        <v>-41.379310344827</v>
       </c>
       <c r="N16" s="14">
-        <v>-84.269662921348</v>
+        <v>-83.168316831683</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E17" s="14">
-        <v>-66.666666666666</v>
+        <v>-40</v>
       </c>
       <c r="F17" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G17" s="15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H17" s="14">
-        <v>-30.769230769230</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="I17" s="15">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J17" s="15">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K17" s="14">
-        <v>-48</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="L17" s="14">
-        <v>-18.75</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M17" s="14">
-        <v>-18.75</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="N17" s="14">
-        <v>-74</v>
+        <v>-69.811320754717</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>1</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+        <v>7</v>
+      </c>
+      <c r="D18" s="15">
+        <v>5</v>
+      </c>
+      <c r="E18" s="14">
+        <v>40</v>
       </c>
       <c r="F18" s="15">
         <v>16</v>
       </c>
       <c r="G18" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H18" s="14">
-        <v>220</v>
+        <v>100</v>
       </c>
       <c r="I18" s="15">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="J18" s="15">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K18" s="14">
-        <v>58.823529411764</v>
+        <v>54.545454545454</v>
       </c>
       <c r="L18" s="14">
-        <v>68.75</v>
+        <v>54.545454545454</v>
       </c>
       <c r="M18" s="14">
-        <v>35</v>
+        <v>54.545454545454</v>
       </c>
       <c r="N18" s="14">
-        <v>-81.506849315068</v>
+        <v>-79.761904761904</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D19" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E19" s="14">
-        <v>160</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F19" s="15">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G19" s="15">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H19" s="14">
-        <v>16.129032258064</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="I19" s="15">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J19" s="15">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="K19" s="14">
-        <v>22</v>
+        <v>10.526315789473</v>
       </c>
       <c r="L19" s="14">
-        <v>24.489795918367</v>
+        <v>12.5</v>
       </c>
       <c r="M19" s="14">
-        <v>0</v>
+        <v>-5.970149253731</v>
       </c>
       <c r="N19" s="14">
-        <v>-45.045045045045</v>
+        <v>-50.78125</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,7 +1098,7 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1116,22 +1116,22 @@
         <v>21</v>
       </c>
       <c r="I20" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J20" s="15">
         <v>3</v>
       </c>
       <c r="K20" s="14">
-        <v>200</v>
+        <v>233.333333333333</v>
       </c>
       <c r="L20" s="14">
-        <v>28.571428571428</v>
+        <v>25</v>
       </c>
       <c r="M20" s="14">
-        <v>200</v>
+        <v>233.333333333333</v>
       </c>
       <c r="N20" s="14">
-        <v>-91.964285714285</v>
+        <v>-92.481203007518</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,72 +1139,72 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>61.538461538461</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="F21" s="17">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G21" s="17">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H21" s="18">
-        <v>32.203389830508</v>
+        <v>9.090909090909</v>
       </c>
       <c r="I21" s="17">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="J21" s="17">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="K21" s="18">
-        <v>11.607142857142</v>
+        <v>6.766917293233</v>
       </c>
       <c r="L21" s="18">
-        <v>12.612612612612</v>
+        <v>5.970149253731</v>
       </c>
       <c r="M21" s="18">
-        <v>-1.574803149606</v>
+        <v>0.709219858156</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.728155339805</v>
+        <v>-75.972927241962</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="15">
         <v>1</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="E22" s="14">
+        <v>-100</v>
       </c>
       <c r="F22" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G22" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" s="14">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="I22" s="15">
         <v>6</v>
       </c>
       <c r="J22" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K22" s="14">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L22" s="14">
         <v>0</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E23" s="14">
-        <v>-80</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G23" s="15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H23" s="14">
-        <v>-61.538461538461</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I23" s="15">
         <v>7</v>
       </c>
       <c r="J23" s="15">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K23" s="14">
-        <v>-66.666666666666</v>
+        <v>-70.833333333333</v>
       </c>
       <c r="L23" s="14">
-        <v>-41.666666666666</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="M23" s="14">
-        <v>-36.363636363636</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D24" s="15">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E24" s="14">
-        <v>-19.444444444444</v>
+        <v>-45.238095238095</v>
       </c>
       <c r="F24" s="15">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G24" s="15">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="H24" s="14">
-        <v>-44.720496894409</v>
+        <v>-49.710982658959</v>
       </c>
       <c r="I24" s="15">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="J24" s="15">
-        <v>214</v>
+        <v>256</v>
       </c>
       <c r="K24" s="14">
-        <v>-17.757009345794</v>
+        <v>-22.265625</v>
       </c>
       <c r="L24" s="14">
-        <v>1.734104046242</v>
+        <v>-0.5</v>
       </c>
       <c r="M24" s="14">
-        <v>36.434108527131</v>
+        <v>39.160839160839</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D25" s="15">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E25" s="14">
-        <v>-37.5</v>
+        <v>-81.818181818181</v>
       </c>
       <c r="F25" s="15">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="G25" s="15">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="H25" s="14">
-        <v>-48.076923076923</v>
+        <v>-65</v>
       </c>
       <c r="I25" s="15">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="J25" s="15">
-        <v>140</v>
+        <v>173</v>
       </c>
       <c r="K25" s="14">
-        <v>-31.428571428571</v>
+        <v>-41.618497109826</v>
       </c>
       <c r="L25" s="14">
-        <v>-15.789473684210</v>
+        <v>-25.735294117647</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>8</v>
       </c>
       <c r="D26" s="15">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E26" s="14">
-        <v>33.333333333333</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="F26" s="15">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G26" s="15">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H26" s="14">
-        <v>72.222222222222</v>
+        <v>32.142857142857</v>
       </c>
       <c r="I26" s="15">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="J26" s="15">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="K26" s="14">
-        <v>66.666666666666</v>
+        <v>28.888888888888</v>
       </c>
       <c r="L26" s="14">
-        <v>35.135135135135</v>
+        <v>41.463414634146</v>
       </c>
       <c r="M26" s="14">
-        <v>38.888888888888</v>
+        <v>34.883720930232</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="15">
+      <c r="C27" s="15">
+        <v>1</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="15">
         <v>2</v>
       </c>
-      <c r="E27" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="15">
-        <v>1</v>
-      </c>
       <c r="G27" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H27" s="14">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="I27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" s="15">
         <v>5</v>
       </c>
       <c r="K27" s="14">
-        <v>-80</v>
+        <v>-60</v>
       </c>
       <c r="L27" s="14">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,28 +1429,28 @@
         <v>20</v>
       </c>
       <c r="D28" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E28" s="14">
         <v>-100</v>
       </c>
       <c r="F28" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G28" s="15">
         <v>6</v>
       </c>
       <c r="H28" s="14">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I28" s="15">
         <v>8</v>
       </c>
       <c r="J28" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K28" s="14">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L28" s="14">
         <v>100</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="15">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="15">
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1484,14 +1484,14 @@
       <c r="H29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="13" t="s">
-        <v>20</v>
+      <c r="I29" s="15">
+        <v>1</v>
       </c>
       <c r="J29" s="15">
         <v>2</v>
       </c>
       <c r="K29" s="14">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>21</v>
@@ -1500,15 +1500,15 @@
         <v>21</v>
       </c>
       <c r="N29" s="14">
-        <v>-100</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="15">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="15">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1525,14 +1525,14 @@
       <c r="H30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I30" s="13" t="s">
-        <v>20</v>
+      <c r="I30" s="15">
+        <v>1</v>
       </c>
       <c r="J30" s="15">
         <v>1</v>
       </c>
       <c r="K30" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>21</v>
@@ -1541,7 +1541,7 @@
         <v>21</v>
       </c>
       <c r="N30" s="14">
-        <v>-100</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="15">
-        <v>1</v>
-      </c>
-      <c r="E31" s="14">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="15">
         <v>2</v>

--- a/data/source/weekly/cs-en-us-024pct.xlsx
+++ b/data/source/weekly/cs-en-us-024pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -892,23 +892,23 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="15">
         <v>1</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="15">
-        <v>2</v>
       </c>
       <c r="G15" s="15">
         <v>2</v>
       </c>
       <c r="H15" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="15">
         <v>2</v>
@@ -933,41 +933,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="15">
         <v>3</v>
       </c>
-      <c r="D16" s="15">
-        <v>4</v>
-      </c>
       <c r="E16" s="14">
-        <v>-25</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G16" s="15">
         <v>8</v>
       </c>
       <c r="H16" s="14">
-        <v>12.5</v>
+        <v>-12.5</v>
       </c>
       <c r="I16" s="15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J16" s="15">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K16" s="14">
-        <v>6.25</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="L16" s="14">
-        <v>-37.037037037037</v>
+        <v>-40</v>
       </c>
       <c r="M16" s="14">
-        <v>-41.379310344827</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="N16" s="14">
-        <v>-83.168316831683</v>
+        <v>-84.615384615384</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D17" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E17" s="14">
-        <v>-40</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F17" s="15">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G17" s="15">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H17" s="14">
-        <v>-46.666666666666</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="I17" s="15">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J17" s="15">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="K17" s="14">
-        <v>-46.666666666666</v>
+        <v>-30.555555555555</v>
       </c>
       <c r="L17" s="14">
-        <v>-11.111111111111</v>
+        <v>13.636363636363</v>
       </c>
       <c r="M17" s="14">
-        <v>-11.111111111111</v>
+        <v>25</v>
       </c>
       <c r="N17" s="14">
-        <v>-69.811320754717</v>
+        <v>-59.016393442622</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D18" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E18" s="14">
-        <v>40</v>
+        <v>-25</v>
       </c>
       <c r="F18" s="15">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G18" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H18" s="14">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I18" s="15">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J18" s="15">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K18" s="14">
-        <v>54.545454545454</v>
+        <v>42.307692307692</v>
       </c>
       <c r="L18" s="14">
-        <v>54.545454545454</v>
+        <v>48</v>
       </c>
       <c r="M18" s="14">
-        <v>54.545454545454</v>
+        <v>54.166666666666</v>
       </c>
       <c r="N18" s="14">
-        <v>-79.761904761904</v>
+        <v>-80.423280423280</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D19" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E19" s="14">
-        <v>-71.428571428571</v>
+        <v>-12.5</v>
       </c>
       <c r="F19" s="15">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G19" s="15">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="H19" s="14">
-        <v>-9.090909090909</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="I19" s="15">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="J19" s="15">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="K19" s="14">
-        <v>10.526315789473</v>
+        <v>9.230769230769</v>
       </c>
       <c r="L19" s="14">
-        <v>12.5</v>
+        <v>-1.388888888888</v>
       </c>
       <c r="M19" s="14">
-        <v>-5.970149253731</v>
+        <v>-5.333333333333</v>
       </c>
       <c r="N19" s="14">
-        <v>-50.78125</v>
+        <v>-53.896103896103</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,38 +1100,38 @@
       <c r="C20" s="15">
         <v>1</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="D20" s="15">
+        <v>1</v>
+      </c>
+      <c r="E20" s="14">
+        <v>0</v>
       </c>
       <c r="F20" s="15">
         <v>7</v>
       </c>
-      <c r="G20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>21</v>
+      <c r="G20" s="15">
+        <v>1</v>
+      </c>
+      <c r="H20" s="14">
+        <v>600</v>
       </c>
       <c r="I20" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J20" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K20" s="14">
-        <v>233.333333333333</v>
+        <v>175</v>
       </c>
       <c r="L20" s="14">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="M20" s="14">
-        <v>233.333333333333</v>
+        <v>120</v>
       </c>
       <c r="N20" s="14">
-        <v>-92.481203007518</v>
+        <v>-92.617449664429</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D21" s="17">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E21" s="18">
-        <v>-19.047619047619</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="F21" s="17">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G21" s="17">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H21" s="18">
-        <v>9.090909090909</v>
+        <v>5.970149253731</v>
       </c>
       <c r="I21" s="17">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="J21" s="17">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="K21" s="18">
-        <v>6.766917293233</v>
+        <v>5.806451612903</v>
       </c>
       <c r="L21" s="18">
-        <v>5.970149253731</v>
+        <v>2.5</v>
       </c>
       <c r="M21" s="18">
-        <v>0.709219858156</v>
+        <v>2.5</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.972927241962</v>
+        <v>-75.811209439528</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="15">
+        <v>1</v>
       </c>
       <c r="D22" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="14">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F22" s="15">
+        <v>2</v>
+      </c>
+      <c r="G22" s="15">
         <v>3</v>
       </c>
-      <c r="G22" s="15">
-        <v>2</v>
-      </c>
       <c r="H22" s="14">
-        <v>50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I22" s="15">
+        <v>7</v>
+      </c>
+      <c r="J22" s="15">
         <v>6</v>
       </c>
-      <c r="J22" s="15">
-        <v>4</v>
-      </c>
       <c r="K22" s="14">
-        <v>50</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L22" s="14">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
       <c r="M22" s="14">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="15">
+        <v>1</v>
       </c>
       <c r="D23" s="15">
         <v>3</v>
       </c>
       <c r="E23" s="14">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F23" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G23" s="15">
         <v>12</v>
       </c>
       <c r="H23" s="14">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="I23" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J23" s="15">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K23" s="14">
-        <v>-70.833333333333</v>
+        <v>-70.370370370370</v>
       </c>
       <c r="L23" s="14">
-        <v>-46.153846153846</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="M23" s="14">
-        <v>-53.333333333333</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D24" s="15">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E24" s="14">
-        <v>-45.238095238095</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="F24" s="15">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="G24" s="15">
         <v>173</v>
       </c>
       <c r="H24" s="14">
-        <v>-49.710982658959</v>
+        <v>-43.352601156069</v>
       </c>
       <c r="I24" s="15">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="J24" s="15">
-        <v>256</v>
+        <v>292</v>
       </c>
       <c r="K24" s="14">
-        <v>-22.265625</v>
+        <v>-23.287671232876</v>
       </c>
       <c r="L24" s="14">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="M24" s="14">
-        <v>39.160839160839</v>
+        <v>44.516129032258</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D25" s="15">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="E25" s="14">
-        <v>-81.818181818181</v>
+        <v>-54.166666666666</v>
       </c>
       <c r="F25" s="15">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G25" s="15">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H25" s="14">
-        <v>-65</v>
+        <v>-65.546218487395</v>
       </c>
       <c r="I25" s="15">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="J25" s="15">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="K25" s="14">
-        <v>-41.618497109826</v>
+        <v>-43.147208121827</v>
       </c>
       <c r="L25" s="14">
-        <v>-25.735294117647</v>
+        <v>-25.333333333333</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D26" s="15">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E26" s="14">
-        <v>-46.666666666666</v>
+        <v>50</v>
       </c>
       <c r="F26" s="15">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G26" s="15">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H26" s="14">
-        <v>32.142857142857</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I26" s="15">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="J26" s="15">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K26" s="14">
-        <v>28.888888888888</v>
+        <v>30.612244897959</v>
       </c>
       <c r="L26" s="14">
-        <v>41.463414634146</v>
+        <v>48.837209302325</v>
       </c>
       <c r="M26" s="14">
-        <v>34.883720930232</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,23 +1384,23 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="15">
         <v>1</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="15">
-        <v>2</v>
       </c>
       <c r="G27" s="15">
         <v>2</v>
       </c>
       <c r="H27" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="15">
         <v>2</v>
@@ -1428,20 +1428,20 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="15">
-        <v>1</v>
-      </c>
-      <c r="E28" s="14">
-        <v>-100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G28" s="15">
         <v>6</v>
       </c>
       <c r="H28" s="14">
-        <v>-16.666666666666</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I28" s="15">
         <v>8</v>
@@ -1453,7 +1453,7 @@
         <v>-11.111111111111</v>
       </c>
       <c r="L28" s="14">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="15">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1507,8 +1507,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="15">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1551,29 +1551,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="15">
+        <v>1</v>
+      </c>
+      <c r="E31" s="14">
+        <v>-100</v>
       </c>
       <c r="F31" s="15">
         <v>2</v>
       </c>
       <c r="G31" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I31" s="15">
         <v>2</v>
       </c>
       <c r="J31" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L31" s="14">
         <v>-33.333333333333</v>

--- a/data/source/weekly/cs-en-us-024pct.xlsx
+++ b/data/source/weekly/cs-en-us-024pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -933,41 +933,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="15">
+        <v>3</v>
       </c>
       <c r="D16" s="15">
         <v>3</v>
       </c>
       <c r="E16" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G16" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H16" s="14">
-        <v>-12.5</v>
+        <v>-20</v>
       </c>
       <c r="I16" s="15">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J16" s="15">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K16" s="14">
-        <v>-5.263157894736</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="L16" s="14">
-        <v>-40</v>
+        <v>-30</v>
       </c>
       <c r="M16" s="14">
-        <v>-47.058823529411</v>
+        <v>-47.5</v>
       </c>
       <c r="N16" s="14">
-        <v>-84.615384615384</v>
+        <v>-83.59375</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D17" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E17" s="14">
-        <v>33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="F17" s="15">
         <v>15</v>
       </c>
       <c r="G17" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H17" s="14">
-        <v>-21.052631578947</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I17" s="15">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J17" s="15">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K17" s="14">
-        <v>-30.555555555555</v>
+        <v>-35</v>
       </c>
       <c r="L17" s="14">
-        <v>13.636363636363</v>
+        <v>0</v>
       </c>
       <c r="M17" s="14">
-        <v>25</v>
+        <v>18.181818181818</v>
       </c>
       <c r="N17" s="14">
-        <v>-59.016393442622</v>
+        <v>-61.764705882352</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D18" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E18" s="14">
-        <v>-25</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F18" s="15">
+        <v>19</v>
+      </c>
+      <c r="G18" s="15">
         <v>15</v>
       </c>
-      <c r="G18" s="15">
-        <v>9</v>
-      </c>
       <c r="H18" s="14">
+        <v>26.666666666666</v>
+      </c>
+      <c r="I18" s="15">
+        <v>45</v>
+      </c>
+      <c r="J18" s="15">
+        <v>32</v>
+      </c>
+      <c r="K18" s="14">
+        <v>40.625</v>
+      </c>
+      <c r="L18" s="14">
         <v>66.666666666666</v>
       </c>
-      <c r="I18" s="15">
-        <v>37</v>
-      </c>
-      <c r="J18" s="15">
-        <v>26</v>
-      </c>
-      <c r="K18" s="14">
-        <v>42.307692307692</v>
-      </c>
-      <c r="L18" s="14">
-        <v>48</v>
-      </c>
       <c r="M18" s="14">
-        <v>54.166666666666</v>
+        <v>73.076923076923</v>
       </c>
       <c r="N18" s="14">
-        <v>-80.423280423280</v>
+        <v>-79.545454545454</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D19" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E19" s="14">
-        <v>-12.5</v>
+        <v>44.444444444444</v>
       </c>
       <c r="F19" s="15">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="G19" s="15">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H19" s="14">
-        <v>-7.142857142857</v>
+        <v>20.689655172413</v>
       </c>
       <c r="I19" s="15">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="J19" s="15">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="K19" s="14">
-        <v>9.230769230769</v>
+        <v>14.864864864864</v>
       </c>
       <c r="L19" s="14">
-        <v>-1.388888888888</v>
+        <v>7.594936708860</v>
       </c>
       <c r="M19" s="14">
-        <v>-5.333333333333</v>
+        <v>0</v>
       </c>
       <c r="N19" s="14">
-        <v>-53.896103896103</v>
+        <v>-53.804347826087</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,13 +1098,13 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>1</v>
-      </c>
-      <c r="D20" s="15">
-        <v>1</v>
-      </c>
-      <c r="E20" s="14">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="15">
         <v>7</v>
@@ -1116,22 +1116,22 @@
         <v>600</v>
       </c>
       <c r="I20" s="15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J20" s="15">
         <v>4</v>
       </c>
       <c r="K20" s="14">
-        <v>175</v>
+        <v>225</v>
       </c>
       <c r="L20" s="14">
-        <v>37.5</v>
+        <v>30</v>
       </c>
       <c r="M20" s="14">
-        <v>120</v>
+        <v>85.714285714285</v>
       </c>
       <c r="N20" s="14">
-        <v>-92.617449664429</v>
+        <v>-91.975308641975</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,54 +1139,54 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D21" s="17">
         <v>22</v>
       </c>
       <c r="E21" s="18">
-        <v>-13.636363636363</v>
+        <v>27.272727272727</v>
       </c>
       <c r="F21" s="17">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="G21" s="17">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="H21" s="18">
-        <v>5.970149253731</v>
+        <v>8.974358974358</v>
       </c>
       <c r="I21" s="17">
-        <v>164</v>
+        <v>192</v>
       </c>
       <c r="J21" s="17">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="K21" s="18">
-        <v>5.806451612903</v>
+        <v>8.474576271186</v>
       </c>
       <c r="L21" s="18">
-        <v>2.5</v>
+        <v>9.714285714285</v>
       </c>
       <c r="M21" s="18">
-        <v>2.5</v>
+        <v>5.494505494505</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.811209439528</v>
+        <v>-75.097276264591</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
-        <v>1</v>
-      </c>
-      <c r="D22" s="15">
-        <v>2</v>
-      </c>
-      <c r="E22" s="14">
-        <v>-50</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="15">
         <v>2</v>
@@ -1210,7 +1210,7 @@
         <v>-12.5</v>
       </c>
       <c r="M22" s="14">
-        <v>133.333333333333</v>
+        <v>40</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E23" s="14">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G23" s="15">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H23" s="14">
-        <v>-75</v>
+        <v>-88.235294117647</v>
       </c>
       <c r="I23" s="15">
         <v>8</v>
       </c>
       <c r="J23" s="15">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K23" s="14">
-        <v>-70.370370370370</v>
+        <v>-75.757575757575</v>
       </c>
       <c r="L23" s="14">
-        <v>-46.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="M23" s="14">
-        <v>-55.555555555555</v>
+        <v>-60</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D24" s="15">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E24" s="14">
-        <v>-27.777777777777</v>
+        <v>-43.243243243243</v>
       </c>
       <c r="F24" s="15">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G24" s="15">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="H24" s="14">
-        <v>-43.352601156069</v>
+        <v>-34.437086092715</v>
       </c>
       <c r="I24" s="15">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="J24" s="15">
-        <v>292</v>
+        <v>329</v>
       </c>
       <c r="K24" s="14">
-        <v>-23.287671232876</v>
+        <v>-25.531914893617</v>
       </c>
       <c r="L24" s="14">
-        <v>0</v>
+        <v>4.700854700854</v>
       </c>
       <c r="M24" s="14">
-        <v>44.516129032258</v>
+        <v>38.418079096045</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D25" s="15">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E25" s="14">
-        <v>-54.166666666666</v>
+        <v>-48</v>
       </c>
       <c r="F25" s="15">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G25" s="15">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="H25" s="14">
-        <v>-65.546218487395</v>
+        <v>-58.490566037735</v>
       </c>
       <c r="I25" s="15">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="J25" s="15">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="K25" s="14">
-        <v>-43.147208121827</v>
+        <v>-43.693693693693</v>
       </c>
       <c r="L25" s="14">
-        <v>-25.333333333333</v>
+        <v>-19.354838709677</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D26" s="15">
         <v>4</v>
       </c>
       <c r="E26" s="14">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="F26" s="15">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="G26" s="15">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H26" s="14">
-        <v>33.333333333333</v>
+        <v>-13.793103448275</v>
       </c>
       <c r="I26" s="15">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="J26" s="15">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K26" s="14">
-        <v>30.612244897959</v>
+        <v>26.415094339622</v>
       </c>
       <c r="L26" s="14">
-        <v>48.837209302325</v>
+        <v>31.372549019607</v>
       </c>
       <c r="M26" s="14">
-        <v>33.333333333333</v>
+        <v>19.642857142857</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="15">
+      <c r="D28" s="15">
         <v>2</v>
+      </c>
+      <c r="E28" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G28" s="15">
         <v>6</v>
       </c>
       <c r="H28" s="14">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="I28" s="15">
         <v>8</v>
       </c>
       <c r="J28" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K28" s="14">
-        <v>-11.111111111111</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="L28" s="14">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1548,35 +1548,35 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="15">
+        <v>1</v>
       </c>
       <c r="D31" s="15">
         <v>1</v>
       </c>
       <c r="E31" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F31" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H31" s="14">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I31" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J31" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K31" s="14">
         <v>0</v>
       </c>
       <c r="L31" s="14">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-024pct.xlsx
+++ b/data/source/weekly/cs-en-us-024pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -904,11 +904,11 @@
       <c r="F15" s="15">
         <v>1</v>
       </c>
-      <c r="G15" s="15">
-        <v>2</v>
-      </c>
-      <c r="H15" s="14">
-        <v>-50</v>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="15">
         <v>2</v>
@@ -923,10 +923,10 @@
         <v>-33.333333333333</v>
       </c>
       <c r="M15" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N15" s="14">
-        <v>-50</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F16" s="15">
         <v>8</v>
       </c>
       <c r="G16" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H16" s="14">
-        <v>-20</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I16" s="15">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J16" s="15">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K16" s="14">
-        <v>-4.545454545454</v>
+        <v>0</v>
       </c>
       <c r="L16" s="14">
-        <v>-30</v>
+        <v>-30.303030303030</v>
       </c>
       <c r="M16" s="14">
-        <v>-47.5</v>
+        <v>-48.888888888888</v>
       </c>
       <c r="N16" s="14">
-        <v>-83.59375</v>
+        <v>-84.137931034482</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D17" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E17" s="14">
-        <v>-50</v>
+        <v>400</v>
       </c>
       <c r="F17" s="15">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G17" s="15">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H17" s="14">
-        <v>-28.571428571428</v>
+        <v>12.5</v>
       </c>
       <c r="I17" s="15">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J17" s="15">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K17" s="14">
-        <v>-35</v>
+        <v>-24.390243902439</v>
       </c>
       <c r="L17" s="14">
-        <v>0</v>
+        <v>14.814814814814</v>
       </c>
       <c r="M17" s="14">
-        <v>18.181818181818</v>
+        <v>34.782608695652</v>
       </c>
       <c r="N17" s="14">
-        <v>-61.764705882352</v>
+        <v>-58.108108108108</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>8</v>
       </c>
       <c r="D18" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E18" s="14">
-        <v>33.333333333333</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F18" s="15">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G18" s="15">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H18" s="14">
-        <v>26.666666666666</v>
+        <v>13.636363636363</v>
       </c>
       <c r="I18" s="15">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J18" s="15">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K18" s="14">
-        <v>40.625</v>
+        <v>35.897435897435</v>
       </c>
       <c r="L18" s="14">
-        <v>66.666666666666</v>
+        <v>82.758620689655</v>
       </c>
       <c r="M18" s="14">
-        <v>73.076923076923</v>
+        <v>82.758620689655</v>
       </c>
       <c r="N18" s="14">
-        <v>-79.545454545454</v>
+        <v>-77.446808510638</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D19" s="15">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E19" s="14">
-        <v>44.444444444444</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F19" s="15">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G19" s="15">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H19" s="14">
-        <v>20.689655172413</v>
+        <v>-13.157894736842</v>
       </c>
       <c r="I19" s="15">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J19" s="15">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="K19" s="14">
-        <v>14.864864864864</v>
+        <v>9.090909090909</v>
       </c>
       <c r="L19" s="14">
-        <v>7.594936708860</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M19" s="14">
-        <v>0</v>
+        <v>4.347826086956</v>
       </c>
       <c r="N19" s="14">
-        <v>-53.804347826087</v>
+        <v>-52</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
+        <v>1</v>
+      </c>
+      <c r="D20" s="15">
+        <v>1</v>
+      </c>
+      <c r="E20" s="14">
+        <v>0</v>
+      </c>
+      <c r="F20" s="15">
+        <v>5</v>
+      </c>
+      <c r="G20" s="15">
         <v>2</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F20" s="15">
-        <v>7</v>
-      </c>
-      <c r="G20" s="15">
-        <v>1</v>
-      </c>
       <c r="H20" s="14">
-        <v>600</v>
+        <v>150</v>
       </c>
       <c r="I20" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J20" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K20" s="14">
-        <v>225</v>
+        <v>180</v>
       </c>
       <c r="L20" s="14">
-        <v>30</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M20" s="14">
-        <v>85.714285714285</v>
+        <v>75</v>
       </c>
       <c r="N20" s="14">
-        <v>-91.975308641975</v>
+        <v>-92</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,75 +1142,75 @@
         <v>28</v>
       </c>
       <c r="D21" s="17">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E21" s="18">
-        <v>27.272727272727</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G21" s="17">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H21" s="18">
-        <v>8.974358974358</v>
+        <v>1.123595505617</v>
       </c>
       <c r="I21" s="17">
-        <v>192</v>
+        <v>219</v>
       </c>
       <c r="J21" s="17">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="K21" s="18">
-        <v>8.474576271186</v>
+        <v>8.955223880597</v>
       </c>
       <c r="L21" s="18">
-        <v>9.714285714285</v>
+        <v>16.489361702127</v>
       </c>
       <c r="M21" s="18">
-        <v>5.494505494505</v>
+        <v>9.5</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.097276264591</v>
+        <v>-73.897497020262</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="C22" s="15">
+        <v>1</v>
+      </c>
+      <c r="D22" s="15">
+        <v>4</v>
+      </c>
+      <c r="E22" s="14">
+        <v>-75</v>
       </c>
       <c r="F22" s="15">
         <v>2</v>
       </c>
       <c r="G22" s="15">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H22" s="14">
-        <v>-33.333333333333</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="I22" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J22" s="15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K22" s="14">
-        <v>16.666666666666</v>
+        <v>-20</v>
       </c>
       <c r="L22" s="14">
-        <v>-12.5</v>
+        <v>0</v>
       </c>
       <c r="M22" s="14">
-        <v>40</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="15">
-        <v>6</v>
-      </c>
-      <c r="E23" s="14">
-        <v>-100</v>
+      <c r="C23" s="15">
+        <v>3</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G23" s="15">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H23" s="14">
-        <v>-88.235294117647</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I23" s="15">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J23" s="15">
         <v>33</v>
       </c>
       <c r="K23" s="14">
-        <v>-75.757575757575</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L23" s="14">
-        <v>-50</v>
+        <v>-31.25</v>
       </c>
       <c r="M23" s="14">
-        <v>-60</v>
+        <v>-47.619047619047</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D24" s="15">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E24" s="14">
-        <v>-43.243243243243</v>
+        <v>12</v>
       </c>
       <c r="F24" s="15">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G24" s="15">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="H24" s="14">
-        <v>-34.437086092715</v>
+        <v>-30</v>
       </c>
       <c r="I24" s="15">
-        <v>245</v>
+        <v>273</v>
       </c>
       <c r="J24" s="15">
-        <v>329</v>
+        <v>354</v>
       </c>
       <c r="K24" s="14">
-        <v>-25.531914893617</v>
+        <v>-22.881355932203</v>
       </c>
       <c r="L24" s="14">
-        <v>4.700854700854</v>
+        <v>7.905138339920</v>
       </c>
       <c r="M24" s="14">
-        <v>38.418079096045</v>
+        <v>40.721649484536</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>13</v>
       </c>
       <c r="D25" s="15">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E25" s="14">
-        <v>-48</v>
+        <v>-18.75</v>
       </c>
       <c r="F25" s="15">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G25" s="15">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="H25" s="14">
-        <v>-58.490566037735</v>
+        <v>-56.122448979591</v>
       </c>
       <c r="I25" s="15">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="J25" s="15">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="K25" s="14">
-        <v>-43.693693693693</v>
+        <v>-42.016806722689</v>
       </c>
       <c r="L25" s="14">
-        <v>-19.354838709677</v>
+        <v>-19.298245614035</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
+        <v>6</v>
+      </c>
+      <c r="D26" s="15">
         <v>2</v>
       </c>
-      <c r="D26" s="15">
-        <v>4</v>
-      </c>
       <c r="E26" s="14">
-        <v>-50</v>
+        <v>200</v>
       </c>
       <c r="F26" s="15">
+        <v>24</v>
+      </c>
+      <c r="G26" s="15">
         <v>25</v>
       </c>
-      <c r="G26" s="15">
-        <v>29</v>
-      </c>
       <c r="H26" s="14">
-        <v>-13.793103448275</v>
+        <v>-4</v>
       </c>
       <c r="I26" s="15">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="J26" s="15">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K26" s="14">
-        <v>26.415094339622</v>
+        <v>34.545454545454</v>
       </c>
       <c r="L26" s="14">
-        <v>31.372549019607</v>
+        <v>32.142857142857</v>
       </c>
       <c r="M26" s="14">
-        <v>19.642857142857</v>
+        <v>10.447761194029</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1396,11 +1396,11 @@
       <c r="F27" s="15">
         <v>1</v>
       </c>
-      <c r="G27" s="15">
-        <v>2</v>
-      </c>
-      <c r="H27" s="14">
-        <v>-50</v>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I27" s="15">
         <v>2</v>
@@ -1412,7 +1412,7 @@
         <v>-60</v>
       </c>
       <c r="L27" s="14">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,7 +1429,7 @@
         <v>20</v>
       </c>
       <c r="D28" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" s="14">
         <v>-100</v>
@@ -1447,10 +1447,10 @@
         <v>8</v>
       </c>
       <c r="J28" s="15">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K28" s="14">
-        <v>-27.272727272727</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L28" s="14">
         <v>0</v>
@@ -1558,25 +1558,25 @@
         <v>0</v>
       </c>
       <c r="F31" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" s="15">
         <v>3</v>
       </c>
       <c r="H31" s="14">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I31" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J31" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K31" s="14">
         <v>0</v>
       </c>
       <c r="L31" s="14">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-024pct.xlsx
+++ b/data/source/weekly/cs-en-us-024pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -895,29 +895,29 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="15">
+      <c r="D15" s="15">
         <v>1</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+      <c r="E15" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="15">
+        <v>1</v>
+      </c>
+      <c r="H15" s="14">
+        <v>-100</v>
       </c>
       <c r="I15" s="15">
         <v>2</v>
       </c>
       <c r="J15" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K15" s="14">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L15" s="14">
         <v>-33.333333333333</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
+        <v>1</v>
+      </c>
+      <c r="D16" s="15">
         <v>2</v>
       </c>
-      <c r="D16" s="15">
-        <v>1</v>
-      </c>
       <c r="E16" s="14">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G16" s="15">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H16" s="14">
-        <v>-27.272727272727</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I16" s="15">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J16" s="15">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K16" s="14">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L16" s="14">
-        <v>-30.303030303030</v>
+        <v>-35.135135135135</v>
       </c>
       <c r="M16" s="14">
-        <v>-48.888888888888</v>
+        <v>-48.936170212766</v>
       </c>
       <c r="N16" s="14">
-        <v>-84.137931034482</v>
+        <v>-85.093167701863</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>5</v>
-      </c>
-      <c r="D17" s="15">
-        <v>1</v>
-      </c>
-      <c r="E17" s="14">
-        <v>400</v>
+        <v>2</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F17" s="15">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G17" s="15">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H17" s="14">
-        <v>12.5</v>
+        <v>45.454545454545</v>
       </c>
       <c r="I17" s="15">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J17" s="15">
         <v>41</v>
       </c>
       <c r="K17" s="14">
-        <v>-24.390243902439</v>
+        <v>-19.512195121951</v>
       </c>
       <c r="L17" s="14">
-        <v>14.814814814814</v>
+        <v>10</v>
       </c>
       <c r="M17" s="14">
-        <v>34.782608695652</v>
+        <v>32</v>
       </c>
       <c r="N17" s="14">
-        <v>-58.108108108108</v>
+        <v>-58.227848101265</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D18" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E18" s="14">
-        <v>14.285714285714</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="15">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G18" s="15">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H18" s="14">
-        <v>13.636363636363</v>
+        <v>0</v>
       </c>
       <c r="I18" s="15">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J18" s="15">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="K18" s="14">
-        <v>35.897435897435</v>
+        <v>26.666666666666</v>
       </c>
       <c r="L18" s="14">
-        <v>82.758620689655</v>
+        <v>90</v>
       </c>
       <c r="M18" s="14">
-        <v>82.758620689655</v>
+        <v>90</v>
       </c>
       <c r="N18" s="14">
-        <v>-77.446808510638</v>
+        <v>-77.647058823529</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,72 +1057,72 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D19" s="15">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E19" s="14">
-        <v>-14.285714285714</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F19" s="15">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G19" s="15">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H19" s="14">
-        <v>-13.157894736842</v>
+        <v>-5</v>
       </c>
       <c r="I19" s="15">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="J19" s="15">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="K19" s="14">
-        <v>9.090909090909</v>
+        <v>5.154639175257</v>
       </c>
       <c r="L19" s="14">
-        <v>14.285714285714</v>
+        <v>9.677419354838</v>
       </c>
       <c r="M19" s="14">
-        <v>4.347826086956</v>
+        <v>0</v>
       </c>
       <c r="N19" s="14">
-        <v>-52</v>
+        <v>-52.336448598130</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>1</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F20" s="15">
+        <v>4</v>
+      </c>
+      <c r="G20" s="15">
+        <v>4</v>
+      </c>
+      <c r="H20" s="14">
         <v>0</v>
-      </c>
-      <c r="F20" s="15">
-        <v>5</v>
-      </c>
-      <c r="G20" s="15">
-        <v>2</v>
-      </c>
-      <c r="H20" s="14">
-        <v>150</v>
       </c>
       <c r="I20" s="15">
         <v>14</v>
       </c>
       <c r="J20" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K20" s="14">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="L20" s="14">
         <v>16.666666666666</v>
@@ -1131,7 +1131,7 @@
         <v>75</v>
       </c>
       <c r="N20" s="14">
-        <v>-92</v>
+        <v>-92.307692307692</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,63 +1139,63 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D21" s="17">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>16.666666666666</v>
+        <v>-30</v>
       </c>
       <c r="F21" s="17">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G21" s="17">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H21" s="18">
-        <v>1.123595505617</v>
+        <v>-1.136363636363</v>
       </c>
       <c r="I21" s="17">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="J21" s="17">
-        <v>201</v>
+        <v>221</v>
       </c>
       <c r="K21" s="18">
-        <v>8.955223880597</v>
+        <v>4.977375565610</v>
       </c>
       <c r="L21" s="18">
-        <v>16.489361702127</v>
+        <v>13.170731707317</v>
       </c>
       <c r="M21" s="18">
-        <v>9.5</v>
+        <v>7.906976744186</v>
       </c>
       <c r="N21" s="18">
-        <v>-73.897497020262</v>
+        <v>-74.250832408435</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
-        <v>1</v>
-      </c>
-      <c r="D22" s="15">
-        <v>4</v>
-      </c>
-      <c r="E22" s="14">
-        <v>-75</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="15">
         <v>2</v>
       </c>
       <c r="G22" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H22" s="14">
-        <v>-71.428571428571</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I22" s="15">
         <v>8</v>
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="14">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="15">
-        <v>3</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D23" s="15">
+        <v>2</v>
+      </c>
+      <c r="E23" s="14">
+        <v>0</v>
       </c>
       <c r="F23" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G23" s="15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H23" s="14">
-        <v>-66.666666666666</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="I23" s="15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J23" s="15">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K23" s="14">
-        <v>-66.666666666666</v>
+        <v>-62.857142857142</v>
       </c>
       <c r="L23" s="14">
-        <v>-31.25</v>
+        <v>-18.75</v>
       </c>
       <c r="M23" s="14">
-        <v>-47.619047619047</v>
+        <v>-45.833333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D24" s="15">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="E24" s="14">
-        <v>12</v>
+        <v>-42.553191489361</v>
       </c>
       <c r="F24" s="15">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G24" s="15">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H24" s="14">
-        <v>-30</v>
+        <v>-29.655172413793</v>
       </c>
       <c r="I24" s="15">
-        <v>273</v>
+        <v>300</v>
       </c>
       <c r="J24" s="15">
-        <v>354</v>
+        <v>401</v>
       </c>
       <c r="K24" s="14">
-        <v>-22.881355932203</v>
+        <v>-25.187032418952</v>
       </c>
       <c r="L24" s="14">
-        <v>7.905138339920</v>
+        <v>4.529616724738</v>
       </c>
       <c r="M24" s="14">
-        <v>40.721649484536</v>
+        <v>42.180094786729</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D25" s="15">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="E25" s="14">
-        <v>-18.75</v>
+        <v>-70</v>
       </c>
       <c r="F25" s="15">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="G25" s="15">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="H25" s="14">
-        <v>-56.122448979591</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="I25" s="15">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="J25" s="15">
-        <v>238</v>
+        <v>278</v>
       </c>
       <c r="K25" s="14">
-        <v>-42.016806722689</v>
+        <v>-46.043165467625</v>
       </c>
       <c r="L25" s="14">
-        <v>-19.298245614035</v>
+        <v>-21.465968586387</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1353,28 +1353,28 @@
         <v>200</v>
       </c>
       <c r="F26" s="15">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G26" s="15">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="H26" s="14">
-        <v>-4</v>
+        <v>83.333333333333</v>
       </c>
       <c r="I26" s="15">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="J26" s="15">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K26" s="14">
-        <v>34.545454545454</v>
+        <v>40.350877192982</v>
       </c>
       <c r="L26" s="14">
-        <v>32.142857142857</v>
+        <v>35.593220338983</v>
       </c>
       <c r="M26" s="14">
-        <v>10.447761194029</v>
+        <v>14.285714285714</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,29 +1387,29 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="15">
+      <c r="D27" s="15">
         <v>1</v>
       </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+      <c r="E27" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" s="15">
+        <v>1</v>
+      </c>
+      <c r="H27" s="14">
+        <v>-100</v>
       </c>
       <c r="I27" s="15">
         <v>2</v>
       </c>
       <c r="J27" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K27" s="14">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L27" s="14">
         <v>-50</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="15">
-        <v>3</v>
-      </c>
-      <c r="E28" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="15">
+        <v>4</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="15">
+        <v>4</v>
       </c>
       <c r="G28" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H28" s="14">
-        <v>-100</v>
+        <v>-20</v>
       </c>
       <c r="I28" s="15">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J28" s="15">
         <v>14</v>
       </c>
       <c r="K28" s="14">
-        <v>-42.857142857142</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L28" s="14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="15">
-        <v>1</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="15">
-        <v>1</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1548,14 +1548,14 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="15">
-        <v>1</v>
-      </c>
-      <c r="D31" s="15">
-        <v>1</v>
-      </c>
-      <c r="E31" s="14">
-        <v>0</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="15">
         <v>2</v>
@@ -1576,7 +1576,7 @@
         <v>0</v>
       </c>
       <c r="L31" s="14">
-        <v>33.333333333333</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-024pct.xlsx
+++ b/data/source/weekly/cs-en-us-024pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>1</v>
       </c>
       <c r="D15" s="15">
         <v>1</v>
       </c>
       <c r="E15" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="F15" s="15">
+        <v>1</v>
       </c>
       <c r="G15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="14">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K15" s="14">
-        <v>-66.666666666666</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L15" s="14">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M15" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N15" s="14">
-        <v>-60</v>
+        <v>-57.142857142857</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" s="14">
         <v>-50</v>
       </c>
       <c r="F16" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G16" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H16" s="14">
-        <v>-33.333333333333</v>
+        <v>-20</v>
       </c>
       <c r="I16" s="15">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J16" s="15">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K16" s="14">
-        <v>-4</v>
+        <v>-10.344827586206</v>
       </c>
       <c r="L16" s="14">
-        <v>-35.135135135135</v>
+        <v>-35</v>
       </c>
       <c r="M16" s="14">
-        <v>-48.936170212766</v>
+        <v>-50</v>
       </c>
       <c r="N16" s="14">
-        <v>-85.093167701863</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,7 +975,7 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>20</v>
@@ -984,31 +984,31 @@
         <v>21</v>
       </c>
       <c r="F17" s="15">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G17" s="15">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H17" s="14">
-        <v>45.454545454545</v>
+        <v>140</v>
       </c>
       <c r="I17" s="15">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J17" s="15">
         <v>41</v>
       </c>
       <c r="K17" s="14">
-        <v>-19.512195121951</v>
+        <v>-12.195121951219</v>
       </c>
       <c r="L17" s="14">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="M17" s="14">
-        <v>32</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N17" s="14">
-        <v>-58.227848101265</v>
+        <v>-58.620689655172</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
+        <v>3</v>
+      </c>
+      <c r="D18" s="15">
         <v>4</v>
       </c>
-      <c r="D18" s="15">
-        <v>6</v>
-      </c>
       <c r="E18" s="14">
-        <v>-33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="F18" s="15">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G18" s="15">
         <v>23</v>
       </c>
       <c r="H18" s="14">
-        <v>0</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="I18" s="15">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J18" s="15">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K18" s="14">
-        <v>26.666666666666</v>
+        <v>20.408163265306</v>
       </c>
       <c r="L18" s="14">
-        <v>90</v>
+        <v>96.666666666666</v>
       </c>
       <c r="M18" s="14">
-        <v>90</v>
+        <v>84.375</v>
       </c>
       <c r="N18" s="14">
-        <v>-77.647058823529</v>
+        <v>-79.078014184397</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D19" s="15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E19" s="14">
-        <v>-22.222222222222</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F19" s="15">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G19" s="15">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H19" s="14">
-        <v>-5</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="I19" s="15">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="J19" s="15">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="K19" s="14">
-        <v>5.154639175257</v>
+        <v>3.669724770642</v>
       </c>
       <c r="L19" s="14">
-        <v>9.677419354838</v>
+        <v>14.141414141414</v>
       </c>
       <c r="M19" s="14">
-        <v>0</v>
+        <v>-1.739130434782</v>
       </c>
       <c r="N19" s="14">
-        <v>-52.336448598130</v>
+        <v>-52.118644067796</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>20</v>
       </c>
       <c r="D20" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="14">
         <v>-100</v>
       </c>
       <c r="F20" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G20" s="15">
         <v>4</v>
       </c>
       <c r="H20" s="14">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="I20" s="15">
         <v>14</v>
       </c>
       <c r="J20" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K20" s="14">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="L20" s="14">
-        <v>16.666666666666</v>
+        <v>7.692307692307</v>
       </c>
       <c r="M20" s="14">
         <v>75</v>
       </c>
       <c r="N20" s="14">
-        <v>-92.307692307692</v>
+        <v>-93.203883495145</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E21" s="18">
-        <v>-30</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="F21" s="17">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G21" s="17">
         <v>88</v>
       </c>
       <c r="H21" s="18">
-        <v>-1.136363636363</v>
+        <v>-2.272727272727</v>
       </c>
       <c r="I21" s="17">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="J21" s="17">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="K21" s="18">
-        <v>4.977375565610</v>
+        <v>3.292181069958</v>
       </c>
       <c r="L21" s="18">
-        <v>13.170731707317</v>
+        <v>15.668202764977</v>
       </c>
       <c r="M21" s="18">
-        <v>7.906976744186</v>
+        <v>5.907172995780</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.250832408435</v>
+        <v>-75.049701789264</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,35 +1182,35 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="15">
+        <v>1</v>
+      </c>
+      <c r="E22" s="14">
+        <v>-100</v>
       </c>
       <c r="F22" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H22" s="14">
-        <v>-66.666666666666</v>
+        <v>-80</v>
       </c>
       <c r="I22" s="15">
         <v>8</v>
       </c>
       <c r="J22" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K22" s="14">
-        <v>-20</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="L22" s="14">
         <v>0</v>
       </c>
       <c r="M22" s="14">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" s="14">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F23" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G23" s="15">
         <v>11</v>
       </c>
       <c r="H23" s="14">
-        <v>-45.454545454545</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="I23" s="15">
         <v>13</v>
       </c>
       <c r="J23" s="15">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K23" s="14">
-        <v>-62.857142857142</v>
+        <v>-65.789473684210</v>
       </c>
       <c r="L23" s="14">
-        <v>-18.75</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="M23" s="14">
-        <v>-45.833333333333</v>
+        <v>-50</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="D24" s="15">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="E24" s="14">
-        <v>-42.553191489361</v>
+        <v>14.705882352941</v>
       </c>
       <c r="F24" s="15">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="G24" s="15">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H24" s="14">
-        <v>-29.655172413793</v>
+        <v>-19.580419580419</v>
       </c>
       <c r="I24" s="15">
-        <v>300</v>
+        <v>338</v>
       </c>
       <c r="J24" s="15">
-        <v>401</v>
+        <v>435</v>
       </c>
       <c r="K24" s="14">
-        <v>-25.187032418952</v>
+        <v>-22.298850574712</v>
       </c>
       <c r="L24" s="14">
-        <v>4.529616724738</v>
+        <v>7.301587301587</v>
       </c>
       <c r="M24" s="14">
-        <v>42.180094786729</v>
+        <v>47.598253275109</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D25" s="15">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E25" s="14">
-        <v>-70</v>
+        <v>-12.5</v>
       </c>
       <c r="F25" s="15">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="G25" s="15">
         <v>105</v>
       </c>
       <c r="H25" s="14">
-        <v>-53.333333333333</v>
+        <v>-44.761904761904</v>
       </c>
       <c r="I25" s="15">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="J25" s="15">
-        <v>278</v>
+        <v>302</v>
       </c>
       <c r="K25" s="14">
-        <v>-46.043165467625</v>
+        <v>-43.708609271523</v>
       </c>
       <c r="L25" s="14">
-        <v>-21.465968586387</v>
+        <v>-18.660287081339</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D26" s="15">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E26" s="14">
-        <v>200</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="F26" s="15">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G26" s="15">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H26" s="14">
-        <v>83.333333333333</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="I26" s="15">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J26" s="15">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="K26" s="14">
-        <v>40.350877192982</v>
+        <v>20.588235294117</v>
       </c>
       <c r="L26" s="14">
-        <v>35.593220338983</v>
+        <v>18.840579710144</v>
       </c>
       <c r="M26" s="14">
-        <v>14.285714285714</v>
+        <v>9.333333333333</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>1</v>
       </c>
       <c r="D27" s="15">
         <v>1</v>
       </c>
       <c r="E27" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="F27" s="15">
+        <v>1</v>
       </c>
       <c r="G27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="14">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J27" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K27" s="14">
-        <v>-66.666666666666</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L27" s="14">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>4</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D28" s="15">
+        <v>3</v>
+      </c>
+      <c r="E28" s="14">
+        <v>-33.333333333333</v>
       </c>
       <c r="F28" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G28" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H28" s="14">
-        <v>-20</v>
+        <v>-25</v>
       </c>
       <c r="I28" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J28" s="15">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K28" s="14">
-        <v>-14.285714285714</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="L28" s="14">
-        <v>20</v>
+        <v>27.272727272727</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1561,10 +1561,10 @@
         <v>2</v>
       </c>
       <c r="G31" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H31" s="14">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I31" s="15">
         <v>4</v>

--- a/data/source/weekly/cs-en-us-024pct.xlsx
+++ b/data/source/weekly/cs-en-us-024pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="15">
         <v>1</v>
       </c>
       <c r="E15" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F15" s="15">
         <v>1</v>
       </c>
       <c r="G15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I15" s="15">
         <v>3</v>
       </c>
       <c r="J15" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K15" s="14">
-        <v>-57.142857142857</v>
+        <v>-62.5</v>
       </c>
       <c r="L15" s="14">
         <v>0</v>
       </c>
       <c r="M15" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N15" s="14">
-        <v>-57.142857142857</v>
+        <v>-62.5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>2</v>
       </c>
       <c r="D16" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E16" s="14">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="F16" s="15">
+        <v>7</v>
+      </c>
+      <c r="G16" s="15">
         <v>8</v>
       </c>
-      <c r="G16" s="15">
-        <v>10</v>
-      </c>
       <c r="H16" s="14">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
       <c r="I16" s="15">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J16" s="15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K16" s="14">
-        <v>-10.344827586206</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="L16" s="14">
-        <v>-35</v>
+        <v>-34.883720930232</v>
       </c>
       <c r="M16" s="14">
-        <v>-50</v>
+        <v>-48.148148148148</v>
       </c>
       <c r="N16" s="14">
-        <v>-85.714285714285</v>
+        <v>-85.929648241206</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>1</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>21</v>
+        <v>4</v>
+      </c>
+      <c r="D17" s="15">
+        <v>6</v>
+      </c>
+      <c r="E17" s="14">
+        <v>-33.333333333333</v>
       </c>
       <c r="F17" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G17" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H17" s="14">
-        <v>140</v>
+        <v>85.714285714285</v>
       </c>
       <c r="I17" s="15">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J17" s="15">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="K17" s="14">
-        <v>-12.195121951219</v>
+        <v>-17.021276595744</v>
       </c>
       <c r="L17" s="14">
-        <v>12.5</v>
+        <v>18.181818181818</v>
       </c>
       <c r="M17" s="14">
-        <v>33.333333333333</v>
+        <v>30</v>
       </c>
       <c r="N17" s="14">
-        <v>-58.620689655172</v>
+        <v>-58.947368421052</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
+        <v>1</v>
+      </c>
+      <c r="D18" s="15">
         <v>3</v>
       </c>
-      <c r="D18" s="15">
-        <v>4</v>
-      </c>
       <c r="E18" s="14">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="F18" s="15">
+        <v>15</v>
+      </c>
+      <c r="G18" s="15">
+        <v>20</v>
+      </c>
+      <c r="H18" s="14">
         <v>-25</v>
       </c>
-      <c r="F18" s="15">
-        <v>22</v>
-      </c>
-      <c r="G18" s="15">
-        <v>23</v>
-      </c>
-      <c r="H18" s="14">
-        <v>-4.347826086956</v>
-      </c>
       <c r="I18" s="15">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J18" s="15">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K18" s="14">
-        <v>20.408163265306</v>
+        <v>15.384615384615</v>
       </c>
       <c r="L18" s="14">
-        <v>96.666666666666</v>
+        <v>81.818181818181</v>
       </c>
       <c r="M18" s="14">
-        <v>84.375</v>
+        <v>76.470588235294</v>
       </c>
       <c r="N18" s="14">
-        <v>-79.078014184397</v>
+        <v>-79.933110367893</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D19" s="15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E19" s="14">
-        <v>-16.666666666666</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="F19" s="15">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G19" s="15">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H19" s="14">
-        <v>-9.090909090909</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="I19" s="15">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="J19" s="15">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="K19" s="14">
-        <v>3.669724770642</v>
+        <v>1.666666666666</v>
       </c>
       <c r="L19" s="14">
-        <v>14.141414141414</v>
+        <v>10.909090909090</v>
       </c>
       <c r="M19" s="14">
-        <v>-1.739130434782</v>
+        <v>-3.174603174603</v>
       </c>
       <c r="N19" s="14">
-        <v>-52.118644067796</v>
+        <v>-53.435114503816</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="15">
+        <v>3</v>
       </c>
       <c r="D20" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="14">
-        <v>-100</v>
+        <v>50</v>
       </c>
       <c r="F20" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G20" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H20" s="14">
-        <v>-25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I20" s="15">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J20" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K20" s="14">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="L20" s="14">
-        <v>7.692307692307</v>
+        <v>30.769230769230</v>
       </c>
       <c r="M20" s="14">
-        <v>75</v>
+        <v>88.888888888888</v>
       </c>
       <c r="N20" s="14">
-        <v>-93.203883495145</v>
+        <v>-92.640692640692</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D21" s="17">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E21" s="18">
-        <v>-22.727272727272</v>
+        <v>-20.833333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="G21" s="17">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H21" s="18">
-        <v>-2.272727272727</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="I21" s="17">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="J21" s="17">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="K21" s="18">
-        <v>3.292181069958</v>
+        <v>0.749063670411</v>
       </c>
       <c r="L21" s="18">
-        <v>15.668202764977</v>
+        <v>14.468085106383</v>
       </c>
       <c r="M21" s="18">
-        <v>5.907172995780</v>
+        <v>4.669260700389</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.049701789264</v>
+        <v>-75.567665758401</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,11 +1182,11 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="15">
-        <v>1</v>
-      </c>
-      <c r="E22" s="14">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="15">
         <v>1</v>
@@ -1207,7 +1207,7 @@
         <v>-27.272727272727</v>
       </c>
       <c r="L22" s="14">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="M22" s="14">
         <v>-11.111111111111</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="15">
+        <v>2</v>
+      </c>
+      <c r="D23" s="15">
         <v>1</v>
       </c>
-      <c r="D23" s="15">
-        <v>3</v>
-      </c>
       <c r="E23" s="14">
-        <v>-66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="F23" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G23" s="15">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H23" s="14">
-        <v>-54.545454545454</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I23" s="15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J23" s="15">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K23" s="14">
-        <v>-65.789473684210</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="L23" s="14">
-        <v>-23.529411764705</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M23" s="14">
-        <v>-50</v>
+        <v>-46.428571428571</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D24" s="15">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E24" s="14">
-        <v>14.705882352941</v>
+        <v>10.526315789473</v>
       </c>
       <c r="F24" s="15">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="G24" s="15">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H24" s="14">
-        <v>-19.580419580419</v>
+        <v>-4.861111111111</v>
       </c>
       <c r="I24" s="15">
-        <v>338</v>
+        <v>381</v>
       </c>
       <c r="J24" s="15">
-        <v>435</v>
+        <v>473</v>
       </c>
       <c r="K24" s="14">
-        <v>-22.298850574712</v>
+        <v>-19.450317124735</v>
       </c>
       <c r="L24" s="14">
-        <v>7.301587301587</v>
+        <v>13.392857142857</v>
       </c>
       <c r="M24" s="14">
-        <v>47.598253275109</v>
+        <v>51.792828685259</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D25" s="15">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E25" s="14">
-        <v>-12.5</v>
+        <v>-20</v>
       </c>
       <c r="F25" s="15">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="G25" s="15">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="H25" s="14">
-        <v>-44.761904761904</v>
+        <v>-37.272727272727</v>
       </c>
       <c r="I25" s="15">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="J25" s="15">
-        <v>302</v>
+        <v>332</v>
       </c>
       <c r="K25" s="14">
-        <v>-43.708609271523</v>
+        <v>-41.566265060241</v>
       </c>
       <c r="L25" s="14">
-        <v>-18.660287081339</v>
+        <v>-12.612612612612</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D26" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E26" s="14">
-        <v>-63.636363636363</v>
+        <v>-91.666666666666</v>
       </c>
       <c r="F26" s="15">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G26" s="15">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="H26" s="14">
-        <v>-10.526315789473</v>
+        <v>-40.740740740740</v>
       </c>
       <c r="I26" s="15">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J26" s="15">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="K26" s="14">
-        <v>20.588235294117</v>
+        <v>5</v>
       </c>
       <c r="L26" s="14">
-        <v>18.840579710144</v>
+        <v>15.068493150684</v>
       </c>
       <c r="M26" s="14">
-        <v>9.333333333333</v>
+        <v>10.526315789473</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,32 +1384,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="15">
         <v>1</v>
       </c>
       <c r="E27" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="15">
         <v>1</v>
       </c>
       <c r="G27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I27" s="15">
         <v>3</v>
       </c>
       <c r="J27" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K27" s="14">
-        <v>-57.142857142857</v>
+        <v>-62.5</v>
       </c>
       <c r="L27" s="14">
         <v>-25</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="15">
         <v>2</v>
       </c>
-      <c r="D28" s="15">
-        <v>3</v>
-      </c>
-      <c r="E28" s="14">
-        <v>-33.333333333333</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
+        <v>8</v>
+      </c>
+      <c r="G28" s="15">
         <v>6</v>
       </c>
-      <c r="G28" s="15">
-        <v>8</v>
-      </c>
       <c r="H28" s="14">
-        <v>-25</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I28" s="15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J28" s="15">
         <v>17</v>
       </c>
       <c r="K28" s="14">
-        <v>-17.647058823529</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="L28" s="14">
-        <v>27.272727272727</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>21</v>
       </c>
       <c r="N29" s="14">
-        <v>-85.714285714285</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,15 +1541,15 @@
         <v>21</v>
       </c>
       <c r="N30" s="14">
-        <v>-85.714285714285</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="15">
+        <v>2</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1561,22 +1561,22 @@
         <v>2</v>
       </c>
       <c r="G31" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I31" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J31" s="15">
         <v>4</v>
       </c>
       <c r="K31" s="14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L31" s="14">
-        <v>-33.333333333333</v>
+        <v>-37.5</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-024pct.xlsx
+++ b/data/source/weekly/cs-en-us-024pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -329,8 +329,8 @@
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#0"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="#,##0"/>
+    <numFmt numFmtId="166" formatCode="#,##0"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
     <numFmt numFmtId="168" formatCode="#,##0.00;&quot;-&quot;#,##0.00"/>
   </numFmts>
   <fonts count="12">
@@ -546,7 +546,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -564,7 +564,7 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -869,8 +869,8 @@
       <c r="H14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I14" s="13" t="s">
-        <v>20</v>
+      <c r="I14" s="14">
+        <v>1</v>
       </c>
       <c r="J14" s="13" t="s">
         <v>20</v>
@@ -881,11 +881,11 @@
       <c r="L14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M14" s="14">
-        <v>-100</v>
-      </c>
-      <c r="N14" s="14">
-        <v>-100</v>
+      <c r="M14" s="15">
+        <v>0</v>
+      </c>
+      <c r="N14" s="15">
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -895,243 +895,243 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
         <v>1</v>
       </c>
-      <c r="E15" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="15">
-        <v>1</v>
-      </c>
-      <c r="G15" s="15">
+      <c r="G15" s="14">
         <v>3</v>
       </c>
-      <c r="H15" s="14">
+      <c r="H15" s="15">
         <v>-66.666666666666</v>
       </c>
-      <c r="I15" s="15">
+      <c r="I15" s="14">
         <v>3</v>
       </c>
-      <c r="J15" s="15">
+      <c r="J15" s="14">
         <v>8</v>
       </c>
-      <c r="K15" s="14">
+      <c r="K15" s="15">
         <v>-62.5</v>
       </c>
-      <c r="L15" s="14">
+      <c r="L15" s="15">
+        <v>-25</v>
+      </c>
+      <c r="M15" s="15">
         <v>0</v>
       </c>
-      <c r="M15" s="14">
-        <v>0</v>
-      </c>
-      <c r="N15" s="14">
-        <v>-62.5</v>
+      <c r="N15" s="15">
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>2</v>
-      </c>
-      <c r="D16" s="15">
+      <c r="C16" s="14">
         <v>1</v>
       </c>
-      <c r="E16" s="14">
-        <v>100</v>
-      </c>
-      <c r="F16" s="15">
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="14">
+        <v>6</v>
+      </c>
+      <c r="G16" s="14">
         <v>7</v>
       </c>
-      <c r="G16" s="15">
-        <v>8</v>
-      </c>
-      <c r="H16" s="14">
-        <v>-12.5</v>
-      </c>
-      <c r="I16" s="15">
-        <v>28</v>
-      </c>
-      <c r="J16" s="15">
+      <c r="H16" s="15">
+        <v>-14.285714285714</v>
+      </c>
+      <c r="I16" s="14">
+        <v>29</v>
+      </c>
+      <c r="J16" s="14">
         <v>30</v>
       </c>
-      <c r="K16" s="14">
-        <v>-6.666666666666</v>
-      </c>
-      <c r="L16" s="14">
-        <v>-34.883720930232</v>
-      </c>
-      <c r="M16" s="14">
-        <v>-48.148148148148</v>
-      </c>
-      <c r="N16" s="14">
-        <v>-85.929648241206</v>
+      <c r="K16" s="15">
+        <v>-3.333333333333</v>
+      </c>
+      <c r="L16" s="15">
+        <v>-35.555555555555</v>
+      </c>
+      <c r="M16" s="15">
+        <v>-47.272727272727</v>
+      </c>
+      <c r="N16" s="15">
+        <v>-86.635944700460</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="15">
-        <v>4</v>
-      </c>
-      <c r="D17" s="15">
-        <v>6</v>
-      </c>
-      <c r="E17" s="14">
+      <c r="C17" s="14">
+        <v>2</v>
+      </c>
+      <c r="D17" s="14">
+        <v>3</v>
+      </c>
+      <c r="E17" s="15">
         <v>-33.333333333333</v>
       </c>
-      <c r="F17" s="15">
-        <v>13</v>
-      </c>
-      <c r="G17" s="15">
-        <v>7</v>
-      </c>
-      <c r="H17" s="14">
-        <v>85.714285714285</v>
-      </c>
-      <c r="I17" s="15">
-        <v>39</v>
-      </c>
-      <c r="J17" s="15">
-        <v>47</v>
-      </c>
-      <c r="K17" s="14">
-        <v>-17.021276595744</v>
-      </c>
-      <c r="L17" s="14">
-        <v>18.181818181818</v>
-      </c>
-      <c r="M17" s="14">
-        <v>30</v>
-      </c>
-      <c r="N17" s="14">
-        <v>-58.947368421052</v>
+      <c r="F17" s="14">
+        <v>11</v>
+      </c>
+      <c r="G17" s="14">
+        <v>9</v>
+      </c>
+      <c r="H17" s="15">
+        <v>22.222222222222</v>
+      </c>
+      <c r="I17" s="14">
+        <v>42</v>
+      </c>
+      <c r="J17" s="14">
+        <v>50</v>
+      </c>
+      <c r="K17" s="15">
+        <v>-16</v>
+      </c>
+      <c r="L17" s="15">
+        <v>16.666666666666</v>
+      </c>
+      <c r="M17" s="15">
+        <v>35.483870967741</v>
+      </c>
+      <c r="N17" s="15">
+        <v>-61.111111111111</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
-        <v>1</v>
-      </c>
-      <c r="D18" s="15">
+      <c r="C18" s="14">
         <v>3</v>
       </c>
-      <c r="E18" s="14">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="F18" s="15">
-        <v>15</v>
-      </c>
-      <c r="G18" s="15">
-        <v>20</v>
-      </c>
-      <c r="H18" s="14">
+      <c r="D18" s="14">
+        <v>4</v>
+      </c>
+      <c r="E18" s="15">
         <v>-25</v>
       </c>
-      <c r="I18" s="15">
-        <v>60</v>
-      </c>
-      <c r="J18" s="15">
-        <v>52</v>
-      </c>
-      <c r="K18" s="14">
-        <v>15.384615384615</v>
-      </c>
-      <c r="L18" s="14">
-        <v>81.818181818181</v>
-      </c>
-      <c r="M18" s="14">
-        <v>76.470588235294</v>
-      </c>
-      <c r="N18" s="14">
-        <v>-79.933110367893</v>
+      <c r="F18" s="14">
+        <v>10</v>
+      </c>
+      <c r="G18" s="14">
+        <v>17</v>
+      </c>
+      <c r="H18" s="15">
+        <v>-41.176470588235</v>
+      </c>
+      <c r="I18" s="14">
+        <v>63</v>
+      </c>
+      <c r="J18" s="14">
+        <v>56</v>
+      </c>
+      <c r="K18" s="15">
+        <v>12.5</v>
+      </c>
+      <c r="L18" s="15">
+        <v>75</v>
+      </c>
+      <c r="M18" s="15">
+        <v>85.294117647058</v>
+      </c>
+      <c r="N18" s="15">
+        <v>-80.434782608695</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="15">
-        <v>9</v>
-      </c>
-      <c r="D19" s="15">
-        <v>11</v>
-      </c>
-      <c r="E19" s="14">
-        <v>-18.181818181818</v>
-      </c>
-      <c r="F19" s="15">
-        <v>38</v>
-      </c>
-      <c r="G19" s="15">
-        <v>46</v>
-      </c>
-      <c r="H19" s="14">
-        <v>-17.391304347826</v>
-      </c>
-      <c r="I19" s="15">
-        <v>122</v>
-      </c>
-      <c r="J19" s="15">
-        <v>120</v>
-      </c>
-      <c r="K19" s="14">
-        <v>1.666666666666</v>
-      </c>
-      <c r="L19" s="14">
-        <v>10.909090909090</v>
-      </c>
-      <c r="M19" s="14">
-        <v>-3.174603174603</v>
-      </c>
-      <c r="N19" s="14">
-        <v>-53.435114503816</v>
+      <c r="C19" s="14">
+        <v>10</v>
+      </c>
+      <c r="D19" s="14">
+        <v>8</v>
+      </c>
+      <c r="E19" s="15">
+        <v>25</v>
+      </c>
+      <c r="F19" s="14">
+        <v>36</v>
+      </c>
+      <c r="G19" s="14">
+        <v>40</v>
+      </c>
+      <c r="H19" s="15">
+        <v>-10</v>
+      </c>
+      <c r="I19" s="14">
+        <v>132</v>
+      </c>
+      <c r="J19" s="14">
+        <v>128</v>
+      </c>
+      <c r="K19" s="15">
+        <v>3.125</v>
+      </c>
+      <c r="L19" s="15">
+        <v>11.864406779661</v>
+      </c>
+      <c r="M19" s="15">
+        <v>-3.649635036496</v>
+      </c>
+      <c r="N19" s="15">
+        <v>-53.356890459364</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>3</v>
-      </c>
-      <c r="D20" s="15">
-        <v>2</v>
-      </c>
-      <c r="E20" s="14">
-        <v>50</v>
-      </c>
-      <c r="F20" s="15">
+      <c r="C20" s="14">
+        <v>1</v>
+      </c>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>0</v>
+      </c>
+      <c r="F20" s="14">
         <v>4</v>
       </c>
-      <c r="G20" s="15">
+      <c r="G20" s="14">
         <v>6</v>
       </c>
-      <c r="H20" s="14">
+      <c r="H20" s="15">
         <v>-33.333333333333</v>
       </c>
-      <c r="I20" s="15">
-        <v>17</v>
-      </c>
-      <c r="J20" s="15">
-        <v>10</v>
-      </c>
-      <c r="K20" s="14">
-        <v>70</v>
-      </c>
-      <c r="L20" s="14">
-        <v>30.769230769230</v>
-      </c>
-      <c r="M20" s="14">
-        <v>88.888888888888</v>
-      </c>
-      <c r="N20" s="14">
-        <v>-92.640692640692</v>
+      <c r="I20" s="14">
+        <v>18</v>
+      </c>
+      <c r="J20" s="14">
+        <v>11</v>
+      </c>
+      <c r="K20" s="15">
+        <v>63.636363636363</v>
+      </c>
+      <c r="L20" s="15">
+        <v>28.571428571428</v>
+      </c>
+      <c r="M20" s="15">
+        <v>80</v>
+      </c>
+      <c r="N20" s="15">
+        <v>-92.996108949416</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D21" s="17">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E21" s="18">
-        <v>-20.833333333333</v>
+        <v>12.5</v>
       </c>
       <c r="F21" s="17">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="G21" s="17">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H21" s="18">
-        <v>-13.333333333333</v>
+        <v>-15.853658536585</v>
       </c>
       <c r="I21" s="17">
-        <v>269</v>
+        <v>288</v>
       </c>
       <c r="J21" s="17">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="K21" s="18">
-        <v>0.749063670411</v>
+        <v>1.766784452296</v>
       </c>
       <c r="L21" s="18">
-        <v>14.468085106383</v>
+        <v>13.833992094861</v>
       </c>
       <c r="M21" s="18">
-        <v>4.669260700389</v>
+        <v>6.273062730627</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.567665758401</v>
+        <v>-76.059850374064</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,34 +1182,34 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="15">
+      <c r="D22" s="14">
         <v>1</v>
       </c>
-      <c r="G22" s="15">
-        <v>5</v>
-      </c>
-      <c r="H22" s="14">
-        <v>-80</v>
-      </c>
-      <c r="I22" s="15">
+      <c r="E22" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="14">
+        <v>2</v>
+      </c>
+      <c r="H22" s="15">
+        <v>-100</v>
+      </c>
+      <c r="I22" s="14">
         <v>8</v>
       </c>
-      <c r="J22" s="15">
-        <v>11</v>
-      </c>
-      <c r="K22" s="14">
-        <v>-27.272727272727</v>
-      </c>
-      <c r="L22" s="14">
+      <c r="J22" s="14">
+        <v>12</v>
+      </c>
+      <c r="K22" s="15">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="L22" s="15">
         <v>-20</v>
       </c>
-      <c r="M22" s="14">
+      <c r="M22" s="15">
         <v>-11.111111111111</v>
       </c>
       <c r="N22" s="13" t="s">
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="14">
         <v>2</v>
       </c>
-      <c r="D23" s="15">
-        <v>1</v>
-      </c>
-      <c r="E23" s="14">
-        <v>100</v>
-      </c>
-      <c r="F23" s="15">
+      <c r="D23" s="14">
+        <v>2</v>
+      </c>
+      <c r="E23" s="15">
+        <v>0</v>
+      </c>
+      <c r="F23" s="14">
         <v>7</v>
       </c>
-      <c r="G23" s="15">
-        <v>6</v>
-      </c>
-      <c r="H23" s="14">
-        <v>16.666666666666</v>
-      </c>
-      <c r="I23" s="15">
-        <v>15</v>
-      </c>
-      <c r="J23" s="15">
-        <v>39</v>
-      </c>
-      <c r="K23" s="14">
-        <v>-61.538461538461</v>
-      </c>
-      <c r="L23" s="14">
-        <v>-16.666666666666</v>
-      </c>
-      <c r="M23" s="14">
-        <v>-46.428571428571</v>
+      <c r="G23" s="14">
+        <v>8</v>
+      </c>
+      <c r="H23" s="15">
+        <v>-12.5</v>
+      </c>
+      <c r="I23" s="14">
+        <v>18</v>
+      </c>
+      <c r="J23" s="14">
+        <v>41</v>
+      </c>
+      <c r="K23" s="15">
+        <v>-56.097560975609</v>
+      </c>
+      <c r="L23" s="15">
+        <v>-18.181818181818</v>
+      </c>
+      <c r="M23" s="15">
+        <v>-35.714285714285</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1261,38 +1261,38 @@
       <c r="A24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="15">
-        <v>42</v>
-      </c>
-      <c r="D24" s="15">
-        <v>38</v>
-      </c>
-      <c r="E24" s="14">
-        <v>10.526315789473</v>
-      </c>
-      <c r="F24" s="15">
-        <v>137</v>
-      </c>
-      <c r="G24" s="15">
-        <v>144</v>
-      </c>
-      <c r="H24" s="14">
-        <v>-4.861111111111</v>
-      </c>
-      <c r="I24" s="15">
-        <v>381</v>
-      </c>
-      <c r="J24" s="15">
-        <v>473</v>
-      </c>
-      <c r="K24" s="14">
-        <v>-19.450317124735</v>
-      </c>
-      <c r="L24" s="14">
-        <v>13.392857142857</v>
-      </c>
-      <c r="M24" s="14">
-        <v>51.792828685259</v>
+      <c r="C24" s="14">
+        <v>39</v>
+      </c>
+      <c r="D24" s="14">
+        <v>36</v>
+      </c>
+      <c r="E24" s="15">
+        <v>8.333333333333</v>
+      </c>
+      <c r="F24" s="14">
+        <v>148</v>
+      </c>
+      <c r="G24" s="14">
+        <v>155</v>
+      </c>
+      <c r="H24" s="15">
+        <v>-4.516129032258</v>
+      </c>
+      <c r="I24" s="14">
+        <v>420</v>
+      </c>
+      <c r="J24" s="14">
+        <v>509</v>
+      </c>
+      <c r="K24" s="15">
+        <v>-17.485265225933</v>
+      </c>
+      <c r="L24" s="15">
+        <v>17.977528089887</v>
+      </c>
+      <c r="M24" s="15">
+        <v>60.919540229885</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="15">
-        <v>24</v>
-      </c>
-      <c r="D25" s="15">
-        <v>30</v>
-      </c>
-      <c r="E25" s="14">
-        <v>-20</v>
-      </c>
-      <c r="F25" s="15">
-        <v>69</v>
-      </c>
-      <c r="G25" s="15">
-        <v>110</v>
-      </c>
-      <c r="H25" s="14">
-        <v>-37.272727272727</v>
-      </c>
-      <c r="I25" s="15">
-        <v>194</v>
-      </c>
-      <c r="J25" s="15">
-        <v>332</v>
-      </c>
-      <c r="K25" s="14">
-        <v>-41.566265060241</v>
-      </c>
-      <c r="L25" s="14">
-        <v>-12.612612612612</v>
+      <c r="C25" s="14">
+        <v>28</v>
+      </c>
+      <c r="D25" s="14">
+        <v>27</v>
+      </c>
+      <c r="E25" s="15">
+        <v>3.703703703703</v>
+      </c>
+      <c r="F25" s="14">
+        <v>83</v>
+      </c>
+      <c r="G25" s="14">
+        <v>121</v>
+      </c>
+      <c r="H25" s="15">
+        <v>-31.404958677686</v>
+      </c>
+      <c r="I25" s="14">
+        <v>221</v>
+      </c>
+      <c r="J25" s="14">
+        <v>359</v>
+      </c>
+      <c r="K25" s="15">
+        <v>-38.440111420612</v>
+      </c>
+      <c r="L25" s="15">
+        <v>-4.741379310344</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1343,38 +1343,38 @@
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="15">
-        <v>1</v>
-      </c>
-      <c r="D26" s="15">
-        <v>12</v>
-      </c>
-      <c r="E26" s="14">
-        <v>-91.666666666666</v>
-      </c>
-      <c r="F26" s="15">
-        <v>16</v>
-      </c>
-      <c r="G26" s="15">
+      <c r="C26" s="14">
+        <v>5</v>
+      </c>
+      <c r="D26" s="14">
+        <v>2</v>
+      </c>
+      <c r="E26" s="15">
+        <v>150</v>
+      </c>
+      <c r="F26" s="14">
+        <v>15</v>
+      </c>
+      <c r="G26" s="14">
         <v>27</v>
       </c>
-      <c r="H26" s="14">
-        <v>-40.740740740740</v>
-      </c>
-      <c r="I26" s="15">
-        <v>84</v>
-      </c>
-      <c r="J26" s="15">
-        <v>80</v>
-      </c>
-      <c r="K26" s="14">
-        <v>5</v>
-      </c>
-      <c r="L26" s="14">
-        <v>15.068493150684</v>
-      </c>
-      <c r="M26" s="14">
-        <v>10.526315789473</v>
+      <c r="H26" s="15">
+        <v>-44.444444444444</v>
+      </c>
+      <c r="I26" s="14">
+        <v>89</v>
+      </c>
+      <c r="J26" s="14">
+        <v>82</v>
+      </c>
+      <c r="K26" s="15">
+        <v>8.536585365853</v>
+      </c>
+      <c r="L26" s="15">
+        <v>20.270270270270</v>
+      </c>
+      <c r="M26" s="15">
+        <v>9.876543209876</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
         <v>1</v>
       </c>
-      <c r="E27" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="15">
-        <v>1</v>
-      </c>
-      <c r="G27" s="15">
+      <c r="G27" s="14">
         <v>3</v>
       </c>
-      <c r="H27" s="14">
+      <c r="H27" s="15">
         <v>-66.666666666666</v>
       </c>
-      <c r="I27" s="15">
+      <c r="I27" s="14">
         <v>3</v>
       </c>
-      <c r="J27" s="15">
+      <c r="J27" s="14">
         <v>8</v>
       </c>
-      <c r="K27" s="14">
+      <c r="K27" s="15">
         <v>-62.5</v>
       </c>
-      <c r="L27" s="14">
-        <v>-25</v>
+      <c r="L27" s="15">
+        <v>-50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>2</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="15">
-        <v>8</v>
-      </c>
-      <c r="G28" s="15">
-        <v>6</v>
-      </c>
-      <c r="H28" s="14">
-        <v>33.333333333333</v>
-      </c>
-      <c r="I28" s="15">
-        <v>16</v>
-      </c>
-      <c r="J28" s="15">
+      <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
+      </c>
+      <c r="F28" s="14">
+        <v>9</v>
+      </c>
+      <c r="G28" s="14">
+        <v>4</v>
+      </c>
+      <c r="H28" s="15">
+        <v>125</v>
+      </c>
+      <c r="I28" s="14">
         <v>17</v>
       </c>
-      <c r="K28" s="14">
-        <v>-5.882352941176</v>
-      </c>
-      <c r="L28" s="14">
-        <v>33.333333333333</v>
+      <c r="J28" s="14">
+        <v>18</v>
+      </c>
+      <c r="K28" s="15">
+        <v>-5.555555555555</v>
+      </c>
+      <c r="L28" s="15">
+        <v>41.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1484,14 +1484,14 @@
       <c r="H29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="15">
-        <v>1</v>
-      </c>
-      <c r="J29" s="15">
+      <c r="I29" s="14">
         <v>2</v>
       </c>
-      <c r="K29" s="14">
-        <v>-50</v>
+      <c r="J29" s="14">
+        <v>2</v>
+      </c>
+      <c r="K29" s="15">
+        <v>0</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>21</v>
@@ -1499,16 +1499,16 @@
       <c r="M29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N29" s="14">
-        <v>-90</v>
+      <c r="N29" s="15">
+        <v>-81.818181818181</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1525,14 +1525,14 @@
       <c r="H30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I30" s="15">
+      <c r="I30" s="14">
+        <v>2</v>
+      </c>
+      <c r="J30" s="14">
         <v>1</v>
       </c>
-      <c r="J30" s="15">
-        <v>1</v>
-      </c>
-      <c r="K30" s="14">
-        <v>0</v>
+      <c r="K30" s="15">
+        <v>100</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>21</v>
@@ -1540,43 +1540,43 @@
       <c r="M30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N30" s="14">
-        <v>-90</v>
+      <c r="N30" s="15">
+        <v>-81.818181818181</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="15">
+      <c r="C31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="14">
         <v>2</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="15">
-        <v>2</v>
-      </c>
-      <c r="G31" s="15">
-        <v>1</v>
-      </c>
-      <c r="H31" s="14">
-        <v>100</v>
-      </c>
-      <c r="I31" s="15">
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I31" s="14">
         <v>5</v>
       </c>
-      <c r="J31" s="15">
+      <c r="J31" s="14">
         <v>4</v>
       </c>
-      <c r="K31" s="14">
+      <c r="K31" s="15">
         <v>25</v>
       </c>
-      <c r="L31" s="14">
-        <v>-37.5</v>
+      <c r="L31" s="15">
+        <v>-50</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1742,31 +1742,31 @@
       <c r="A39" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="14">
         <v>18</v>
       </c>
-      <c r="E39" s="15">
+      <c r="E39" s="14">
         <v>23</v>
       </c>
-      <c r="G39" s="15">
+      <c r="G39" s="14">
         <v>2</v>
       </c>
-      <c r="I39" s="15">
+      <c r="I39" s="14">
         <v>3</v>
       </c>
-      <c r="J39" s="15">
+      <c r="J39" s="14">
         <v>1</v>
       </c>
-      <c r="K39" s="14">
+      <c r="K39" s="15">
         <v>-66.666666666666</v>
       </c>
-      <c r="L39" s="14">
+      <c r="L39" s="15">
         <v>-50</v>
       </c>
-      <c r="M39" s="14">
+      <c r="M39" s="15">
         <v>-95.652173913043</v>
       </c>
-      <c r="N39" s="14">
+      <c r="N39" s="15">
         <v>-94.444444444444</v>
       </c>
     </row>
@@ -1774,31 +1774,31 @@
       <c r="A40" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="15">
+      <c r="C40" s="14">
         <v>34</v>
       </c>
-      <c r="E40" s="15">
+      <c r="E40" s="14">
         <v>35</v>
       </c>
-      <c r="G40" s="15">
+      <c r="G40" s="14">
         <v>17</v>
       </c>
-      <c r="I40" s="15">
+      <c r="I40" s="14">
         <v>12</v>
       </c>
-      <c r="J40" s="15">
+      <c r="J40" s="14">
         <v>18</v>
       </c>
-      <c r="K40" s="14">
+      <c r="K40" s="15">
         <v>50</v>
       </c>
-      <c r="L40" s="14">
+      <c r="L40" s="15">
         <v>5.882352941176</v>
       </c>
-      <c r="M40" s="14">
+      <c r="M40" s="15">
         <v>-48.571428571428</v>
       </c>
-      <c r="N40" s="14">
+      <c r="N40" s="15">
         <v>-47.058823529411</v>
       </c>
     </row>
@@ -1806,31 +1806,31 @@
       <c r="A41" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="14">
         <v>1193</v>
       </c>
-      <c r="E41" s="15">
+      <c r="E41" s="14">
         <v>889</v>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="14">
         <v>430</v>
       </c>
-      <c r="I41" s="15">
+      <c r="I41" s="14">
         <v>341</v>
       </c>
-      <c r="J41" s="15">
+      <c r="J41" s="14">
         <v>96</v>
       </c>
-      <c r="K41" s="14">
+      <c r="K41" s="15">
         <v>-71.847507331378</v>
       </c>
-      <c r="L41" s="14">
+      <c r="L41" s="15">
         <v>-77.674418604651</v>
       </c>
-      <c r="M41" s="14">
+      <c r="M41" s="15">
         <v>-89.201349831271</v>
       </c>
-      <c r="N41" s="14">
+      <c r="N41" s="15">
         <v>-91.953059513830</v>
       </c>
     </row>
@@ -1838,31 +1838,31 @@
       <c r="A42" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="14">
         <v>259</v>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="14">
         <v>460</v>
       </c>
-      <c r="G42" s="15">
+      <c r="G42" s="14">
         <v>271</v>
       </c>
-      <c r="I42" s="15">
+      <c r="I42" s="14">
         <v>181</v>
       </c>
-      <c r="J42" s="15">
+      <c r="J42" s="14">
         <v>192</v>
       </c>
-      <c r="K42" s="14">
+      <c r="K42" s="15">
         <v>6.077348066298</v>
       </c>
-      <c r="L42" s="14">
+      <c r="L42" s="15">
         <v>-29.151291512915</v>
       </c>
-      <c r="M42" s="14">
+      <c r="M42" s="15">
         <v>-58.260869565217</v>
       </c>
-      <c r="N42" s="14">
+      <c r="N42" s="15">
         <v>-25.868725868725</v>
       </c>
     </row>
@@ -1870,31 +1870,31 @@
       <c r="A43" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="14">
         <v>1360</v>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="14">
         <v>1071</v>
       </c>
-      <c r="G43" s="15">
+      <c r="G43" s="14">
         <v>419</v>
       </c>
-      <c r="I43" s="15">
+      <c r="I43" s="14">
         <v>251</v>
       </c>
-      <c r="J43" s="15">
+      <c r="J43" s="14">
         <v>208</v>
       </c>
-      <c r="K43" s="14">
+      <c r="K43" s="15">
         <v>-17.131474103585</v>
       </c>
-      <c r="L43" s="14">
+      <c r="L43" s="15">
         <v>-50.357995226730</v>
       </c>
-      <c r="M43" s="14">
+      <c r="M43" s="15">
         <v>-80.578898225957</v>
       </c>
-      <c r="N43" s="14">
+      <c r="N43" s="15">
         <v>-84.705882352941</v>
       </c>
     </row>
@@ -1902,31 +1902,31 @@
       <c r="A44" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="14">
         <v>1267</v>
       </c>
-      <c r="E44" s="15">
+      <c r="E44" s="14">
         <v>1126</v>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="14">
         <v>523</v>
       </c>
-      <c r="I44" s="15">
+      <c r="I44" s="14">
         <v>522</v>
       </c>
-      <c r="J44" s="15">
+      <c r="J44" s="14">
         <v>536</v>
       </c>
-      <c r="K44" s="14">
+      <c r="K44" s="15">
         <v>2.681992337164</v>
       </c>
-      <c r="L44" s="14">
+      <c r="L44" s="15">
         <v>2.485659655831</v>
       </c>
-      <c r="M44" s="14">
+      <c r="M44" s="15">
         <v>-52.397868561278</v>
       </c>
-      <c r="N44" s="14">
+      <c r="N44" s="15">
         <v>-57.695343330702</v>
       </c>
     </row>
@@ -1934,31 +1934,31 @@
       <c r="A45" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="14">
         <v>1510</v>
       </c>
-      <c r="E45" s="15">
+      <c r="E45" s="14">
         <v>990</v>
       </c>
-      <c r="G45" s="15">
+      <c r="G45" s="14">
         <v>356</v>
       </c>
-      <c r="I45" s="15">
+      <c r="I45" s="14">
         <v>193</v>
       </c>
-      <c r="J45" s="15">
+      <c r="J45" s="14">
         <v>46</v>
       </c>
-      <c r="K45" s="14">
+      <c r="K45" s="15">
         <v>-76.165803108808</v>
       </c>
-      <c r="L45" s="14">
+      <c r="L45" s="15">
         <v>-87.078651685393</v>
       </c>
-      <c r="M45" s="14">
+      <c r="M45" s="15">
         <v>-95.353535353535</v>
       </c>
-      <c r="N45" s="14">
+      <c r="N45" s="15">
         <v>-96.953642384106</v>
       </c>
     </row>

--- a/data/source/weekly/cs-en-us-024pct.xlsx
+++ b/data/source/weekly/cs-en-us-024pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -851,32 +851,32 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="14">
         <v>1</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="14">
         <v>1</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>0</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
       </c>
-      <c r="J14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>21</v>
+      <c r="J14" s="14">
+        <v>1</v>
+      </c>
+      <c r="K14" s="15">
+        <v>0</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>21</v>
@@ -885,15 +885,15 @@
         <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-85.714285714285</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,72 +902,72 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" s="14">
         <v>8</v>
       </c>
       <c r="K15" s="15">
-        <v>-62.5</v>
+        <v>-50</v>
       </c>
       <c r="L15" s="15">
-        <v>-25</v>
+        <v>-20</v>
       </c>
       <c r="M15" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>-66.666666666666</v>
+        <v>-55.555555555555</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="14">
         <v>1</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="E16" s="15">
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
+        <v>5</v>
+      </c>
+      <c r="G16" s="14">
         <v>6</v>
       </c>
-      <c r="G16" s="14">
-        <v>7</v>
-      </c>
       <c r="H16" s="15">
-        <v>-14.285714285714</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I16" s="14">
         <v>29</v>
       </c>
       <c r="J16" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K16" s="15">
-        <v>-3.333333333333</v>
+        <v>-6.451612903225</v>
       </c>
       <c r="L16" s="15">
-        <v>-35.555555555555</v>
+        <v>-38.297872340425</v>
       </c>
       <c r="M16" s="15">
-        <v>-47.272727272727</v>
+        <v>-51.666666666666</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.635944700460</v>
+        <v>-87.763713080168</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E17" s="15">
-        <v>-33.333333333333</v>
+        <v>300</v>
       </c>
       <c r="F17" s="14">
         <v>11</v>
       </c>
       <c r="G17" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H17" s="15">
-        <v>22.222222222222</v>
+        <v>10</v>
       </c>
       <c r="I17" s="14">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J17" s="14">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K17" s="15">
-        <v>-16</v>
+        <v>-9.803921568627</v>
       </c>
       <c r="L17" s="15">
-        <v>16.666666666666</v>
+        <v>21.052631578947</v>
       </c>
       <c r="M17" s="15">
-        <v>35.483870967741</v>
+        <v>43.75</v>
       </c>
       <c r="N17" s="15">
-        <v>-61.111111111111</v>
+        <v>-60.344827586206</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
         <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>-25</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G18" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H18" s="15">
-        <v>-41.176470588235</v>
+        <v>-40</v>
       </c>
       <c r="I18" s="14">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J18" s="14">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K18" s="15">
-        <v>12.5</v>
+        <v>8.333333333333</v>
       </c>
       <c r="L18" s="15">
-        <v>75</v>
+        <v>62.5</v>
       </c>
       <c r="M18" s="15">
-        <v>85.294117647058</v>
+        <v>71.052631578947</v>
       </c>
       <c r="N18" s="15">
-        <v>-80.434782608695</v>
+        <v>-80.938416422287</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E19" s="15">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F19" s="14">
         <v>36</v>
       </c>
       <c r="G19" s="14">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H19" s="15">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="I19" s="14">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="J19" s="14">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K19" s="15">
-        <v>3.125</v>
+        <v>4.511278195488</v>
       </c>
       <c r="L19" s="15">
-        <v>11.864406779661</v>
+        <v>12.096774193548</v>
       </c>
       <c r="M19" s="15">
-        <v>-3.649635036496</v>
+        <v>-6.081081081081</v>
       </c>
       <c r="N19" s="15">
-        <v>-53.356890459364</v>
+        <v>-54.276315789473</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
-      </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
+        <v>10</v>
+      </c>
+      <c r="G20" s="14">
         <v>4</v>
       </c>
-      <c r="G20" s="14">
-        <v>6</v>
-      </c>
       <c r="H20" s="15">
-        <v>-33.333333333333</v>
+        <v>150</v>
       </c>
       <c r="I20" s="14">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J20" s="14">
         <v>11</v>
       </c>
       <c r="K20" s="15">
-        <v>63.636363636363</v>
+        <v>118.181818181818</v>
       </c>
       <c r="L20" s="15">
-        <v>28.571428571428</v>
+        <v>71.428571428571</v>
       </c>
       <c r="M20" s="15">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.996108949416</v>
+        <v>-91.397849462365</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D21" s="17">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E21" s="18">
-        <v>12.5</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G21" s="17">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H21" s="18">
-        <v>-15.853658536585</v>
+        <v>0</v>
       </c>
       <c r="I21" s="17">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="J21" s="17">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="K21" s="18">
-        <v>1.766784452296</v>
+        <v>4.406779661016</v>
       </c>
       <c r="L21" s="18">
-        <v>13.833992094861</v>
+        <v>14.925373134328</v>
       </c>
       <c r="M21" s="18">
-        <v>6.273062730627</v>
+        <v>5.479452054794</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.059850374064</v>
+        <v>-76.197836166924</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,11 +1182,11 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
@@ -1210,7 +1210,7 @@
         <v>-20</v>
       </c>
       <c r="M22" s="15">
-        <v>-11.111111111111</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1224,34 +1224,34 @@
         <v>2</v>
       </c>
       <c r="D23" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F23" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G23" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H23" s="15">
-        <v>-12.5</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I23" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J23" s="14">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K23" s="15">
-        <v>-56.097560975609</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="L23" s="15">
-        <v>-18.181818181818</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="M23" s="15">
-        <v>-35.714285714285</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D24" s="14">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E24" s="15">
-        <v>8.333333333333</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F24" s="14">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="G24" s="14">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="H24" s="15">
-        <v>-4.516129032258</v>
+        <v>12.318840579710</v>
       </c>
       <c r="I24" s="14">
-        <v>420</v>
+        <v>456</v>
       </c>
       <c r="J24" s="14">
-        <v>509</v>
+        <v>539</v>
       </c>
       <c r="K24" s="15">
-        <v>-17.485265225933</v>
+        <v>-15.398886827458</v>
       </c>
       <c r="L24" s="15">
-        <v>17.977528089887</v>
+        <v>20.634920634920</v>
       </c>
       <c r="M24" s="15">
-        <v>60.919540229885</v>
+        <v>60</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D25" s="14">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E25" s="15">
-        <v>3.703703703703</v>
+        <v>15.789473684210</v>
       </c>
       <c r="F25" s="14">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="G25" s="14">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="H25" s="15">
-        <v>-31.404958677686</v>
+        <v>-4</v>
       </c>
       <c r="I25" s="14">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="J25" s="14">
-        <v>359</v>
+        <v>378</v>
       </c>
       <c r="K25" s="15">
-        <v>-38.440111420612</v>
+        <v>-35.185185185185</v>
       </c>
       <c r="L25" s="15">
-        <v>-4.741379310344</v>
+        <v>0.823045267489</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D26" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E26" s="15">
-        <v>150</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G26" s="14">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H26" s="15">
-        <v>-44.444444444444</v>
+        <v>-38.709677419354</v>
       </c>
       <c r="I26" s="14">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="J26" s="14">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="K26" s="15">
-        <v>8.536585365853</v>
+        <v>10.227272727272</v>
       </c>
       <c r="L26" s="15">
-        <v>20.270270270270</v>
+        <v>21.25</v>
       </c>
       <c r="M26" s="15">
-        <v>9.876543209876</v>
+        <v>12.790697674418</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J27" s="14">
         <v>8</v>
       </c>
       <c r="K27" s="15">
-        <v>-62.5</v>
+        <v>-50</v>
       </c>
       <c r="L27" s="15">
-        <v>-50</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
+        <v>100</v>
+      </c>
+      <c r="F28" s="14">
+        <v>7</v>
+      </c>
+      <c r="G28" s="14">
+        <v>5</v>
+      </c>
+      <c r="H28" s="15">
+        <v>40</v>
+      </c>
+      <c r="I28" s="14">
+        <v>19</v>
+      </c>
+      <c r="J28" s="14">
+        <v>19</v>
+      </c>
+      <c r="K28" s="15">
         <v>0</v>
       </c>
-      <c r="F28" s="14">
-        <v>9</v>
-      </c>
-      <c r="G28" s="14">
-        <v>4</v>
-      </c>
-      <c r="H28" s="15">
-        <v>125</v>
-      </c>
-      <c r="I28" s="14">
-        <v>17</v>
-      </c>
-      <c r="J28" s="14">
-        <v>18</v>
-      </c>
-      <c r="K28" s="15">
-        <v>-5.555555555555</v>
-      </c>
       <c r="L28" s="15">
-        <v>41.666666666666</v>
+        <v>46.153846153846</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1500,15 +1500,15 @@
         <v>21</v>
       </c>
       <c r="N29" s="15">
-        <v>-81.818181818181</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1541,15 +1541,15 @@
         <v>21</v>
       </c>
       <c r="N30" s="15">
-        <v>-81.818181818181</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1558,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1567,16 +1567,16 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J31" s="14">
         <v>4</v>
       </c>
       <c r="K31" s="15">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="L31" s="15">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-024pct.xlsx
+++ b/data/source/weekly/cs-en-us-024pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="14">
         <v>1</v>
@@ -892,20 +892,20 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="14">
-        <v>2</v>
-      </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="15">
         <v>0</v>
@@ -926,7 +926,7 @@
         <v>33.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>-55.555555555555</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
         <v>-100</v>
       </c>
       <c r="F16" s="14">
+        <v>4</v>
+      </c>
+      <c r="G16" s="14">
         <v>5</v>
       </c>
-      <c r="G16" s="14">
-        <v>6</v>
-      </c>
       <c r="H16" s="15">
-        <v>-16.666666666666</v>
+        <v>-20</v>
       </c>
       <c r="I16" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J16" s="14">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K16" s="15">
-        <v>-6.451612903225</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="L16" s="15">
-        <v>-38.297872340425</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="M16" s="15">
-        <v>-51.666666666666</v>
+        <v>-55.882352941176</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.763713080168</v>
+        <v>-88.188976377952</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>300</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G17" s="14">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H17" s="15">
-        <v>10</v>
+        <v>-12.5</v>
       </c>
       <c r="I17" s="14">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="J17" s="14">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="K17" s="15">
-        <v>-9.803921568627</v>
+        <v>-12.280701754386</v>
       </c>
       <c r="L17" s="15">
-        <v>21.052631578947</v>
+        <v>16.279069767441</v>
       </c>
       <c r="M17" s="15">
-        <v>43.75</v>
+        <v>42.857142857142</v>
       </c>
       <c r="N17" s="15">
-        <v>-60.344827586206</v>
+        <v>-59.349593495935</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1025,31 +1025,31 @@
         <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G18" s="14">
         <v>15</v>
       </c>
       <c r="H18" s="15">
-        <v>-40</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="I18" s="14">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J18" s="14">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K18" s="15">
-        <v>8.333333333333</v>
+        <v>4.6875</v>
       </c>
       <c r="L18" s="15">
-        <v>62.5</v>
+        <v>59.523809523809</v>
       </c>
       <c r="M18" s="15">
-        <v>71.052631578947</v>
+        <v>67.5</v>
       </c>
       <c r="N18" s="15">
-        <v>-80.938416422287</v>
+        <v>-80.965909090909</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,48 +1057,48 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D19" s="14">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E19" s="15">
-        <v>40</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="F19" s="14">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G19" s="14">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H19" s="15">
+        <v>-9.756097560975</v>
+      </c>
+      <c r="I19" s="14">
+        <v>150</v>
+      </c>
+      <c r="J19" s="14">
+        <v>150</v>
+      </c>
+      <c r="K19" s="15">
         <v>0</v>
       </c>
-      <c r="I19" s="14">
-        <v>139</v>
-      </c>
-      <c r="J19" s="14">
-        <v>133</v>
-      </c>
-      <c r="K19" s="15">
-        <v>4.511278195488</v>
-      </c>
       <c r="L19" s="15">
-        <v>12.096774193548</v>
+        <v>13.636363636363</v>
       </c>
       <c r="M19" s="15">
-        <v>-6.081081081081</v>
+        <v>-5.063291139240</v>
       </c>
       <c r="N19" s="15">
-        <v>-54.276315789473</v>
+        <v>-52.229299363057</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>6</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1110,10 +1110,10 @@
         <v>10</v>
       </c>
       <c r="G20" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H20" s="15">
-        <v>150</v>
+        <v>233.333333333333</v>
       </c>
       <c r="I20" s="14">
         <v>24</v>
@@ -1125,13 +1125,13 @@
         <v>118.181818181818</v>
       </c>
       <c r="L20" s="15">
-        <v>71.428571428571</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M20" s="15">
-        <v>140</v>
+        <v>118.181818181818</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.397849462365</v>
+        <v>-92.233009708737</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="E21" s="18">
-        <v>66.666666666666</v>
+        <v>-43.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G21" s="17">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H21" s="18">
-        <v>0</v>
+        <v>-8.536585365853</v>
       </c>
       <c r="I21" s="17">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="J21" s="17">
-        <v>295</v>
+        <v>325</v>
       </c>
       <c r="K21" s="18">
-        <v>4.406779661016</v>
+        <v>0.307692307692</v>
       </c>
       <c r="L21" s="18">
-        <v>14.925373134328</v>
+        <v>12.027491408934</v>
       </c>
       <c r="M21" s="18">
-        <v>5.479452054794</v>
+        <v>3.164556962025</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.197836166924</v>
+        <v>-76.204379562043</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,17 +1182,17 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>3</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G22" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H22" s="15">
         <v>-100</v>
@@ -1201,13 +1201,13 @@
         <v>8</v>
       </c>
       <c r="J22" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K22" s="15">
-        <v>-33.333333333333</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="L22" s="15">
-        <v>-20</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="M22" s="15">
         <v>-27.272727272727</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>-33.333333333333</v>
+        <v>200</v>
       </c>
       <c r="F23" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G23" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H23" s="15">
-        <v>-11.111111111111</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I23" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J23" s="14">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K23" s="15">
-        <v>-54.545454545454</v>
+        <v>-48.888888888888</v>
       </c>
       <c r="L23" s="15">
-        <v>-9.090909090909</v>
+        <v>-11.538461538461</v>
       </c>
       <c r="M23" s="15">
-        <v>-33.333333333333</v>
+        <v>-28.125</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D24" s="14">
         <v>30</v>
       </c>
       <c r="E24" s="15">
-        <v>16.666666666666</v>
+        <v>20</v>
       </c>
       <c r="F24" s="14">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G24" s="14">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H24" s="15">
-        <v>12.318840579710</v>
+        <v>12.686567164179</v>
       </c>
       <c r="I24" s="14">
-        <v>456</v>
+        <v>491</v>
       </c>
       <c r="J24" s="14">
-        <v>539</v>
+        <v>569</v>
       </c>
       <c r="K24" s="15">
-        <v>-15.398886827458</v>
+        <v>-13.708260105448</v>
       </c>
       <c r="L24" s="15">
-        <v>20.634920634920</v>
+        <v>24.936386768447</v>
       </c>
       <c r="M24" s="15">
-        <v>60</v>
+        <v>61.513157894736</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D25" s="14">
         <v>19</v>
       </c>
       <c r="E25" s="15">
-        <v>15.789473684210</v>
+        <v>21.052631578947</v>
       </c>
       <c r="F25" s="14">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G25" s="14">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H25" s="15">
-        <v>-4</v>
+        <v>3.157894736842</v>
       </c>
       <c r="I25" s="14">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="J25" s="14">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="K25" s="15">
-        <v>-35.185185185185</v>
+        <v>-32.493702770780</v>
       </c>
       <c r="L25" s="15">
-        <v>0.823045267489</v>
+        <v>6.772908366533</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
         <v>6</v>
       </c>
       <c r="E26" s="15">
-        <v>33.333333333333</v>
+        <v>83.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G26" s="14">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="H26" s="15">
-        <v>-38.709677419354</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="I26" s="14">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="J26" s="14">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="K26" s="15">
-        <v>10.227272727272</v>
+        <v>14.893617021276</v>
       </c>
       <c r="L26" s="15">
-        <v>21.25</v>
+        <v>30.120481927710</v>
       </c>
       <c r="M26" s="15">
-        <v>12.790697674418</v>
+        <v>22.727272727272</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,20 +1384,20 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="14">
-        <v>2</v>
-      </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="15">
         <v>0</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F28" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>40</v>
+        <v>166.666666666667</v>
       </c>
       <c r="I28" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J28" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L28" s="15">
-        <v>46.153846153846</v>
+        <v>69.230769230769</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1476,7 +1476,7 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1485,13 +1485,13 @@
         <v>21</v>
       </c>
       <c r="I29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J29" s="14">
         <v>2</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>21</v>
@@ -1500,15 +1500,15 @@
         <v>21</v>
       </c>
       <c r="N29" s="15">
-        <v>-83.333333333333</v>
+        <v>-76.923076923076</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1517,7 +1517,7 @@
         <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1526,13 +1526,13 @@
         <v>21</v>
       </c>
       <c r="I30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J30" s="14">
         <v>1</v>
       </c>
       <c r="K30" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>21</v>
@@ -1541,15 +1541,15 @@
         <v>21</v>
       </c>
       <c r="N30" s="15">
-        <v>-83.333333333333</v>
+        <v>-76.923076923076</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1567,16 +1567,16 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J31" s="14">
         <v>4</v>
       </c>
       <c r="K31" s="15">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="L31" s="15">
-        <v>-20</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-024pct.xlsx
+++ b/data/source/weekly/cs-en-us-024pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -895,11 +895,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
@@ -914,13 +914,13 @@
         <v>4</v>
       </c>
       <c r="J15" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K15" s="15">
-        <v>-50</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="L15" s="15">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M15" s="15">
         <v>33.333333333333</v>
@@ -933,14 +933,14 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F16" s="14">
         <v>4</v>
@@ -952,22 +952,22 @@
         <v>-20</v>
       </c>
       <c r="I16" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J16" s="14">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K16" s="15">
-        <v>-11.764705882352</v>
+        <v>-8.571428571428</v>
       </c>
       <c r="L16" s="15">
-        <v>-41.176470588235</v>
+        <v>-40.740740740740</v>
       </c>
       <c r="M16" s="15">
-        <v>-55.882352941176</v>
+        <v>-56.164383561643</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.188976377952</v>
+        <v>-88.278388278388</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
         <v>-33.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G17" s="14">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H17" s="15">
-        <v>-12.5</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="I17" s="14">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J17" s="14">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K17" s="15">
-        <v>-12.280701754386</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="L17" s="15">
-        <v>16.279069767441</v>
+        <v>15.555555555555</v>
       </c>
       <c r="M17" s="15">
-        <v>42.857142857142</v>
+        <v>44.444444444444</v>
       </c>
       <c r="N17" s="15">
-        <v>-59.349593495935</v>
+        <v>-60.606060606060</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G18" s="14">
         <v>15</v>
       </c>
       <c r="H18" s="15">
-        <v>-46.666666666666</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="I18" s="14">
+        <v>71</v>
+      </c>
+      <c r="J18" s="14">
         <v>67</v>
       </c>
-      <c r="J18" s="14">
-        <v>64</v>
-      </c>
       <c r="K18" s="15">
-        <v>4.6875</v>
+        <v>5.970149253731</v>
       </c>
       <c r="L18" s="15">
-        <v>59.523809523809</v>
+        <v>61.363636363636</v>
       </c>
       <c r="M18" s="15">
-        <v>67.5</v>
+        <v>69.047619047619</v>
       </c>
       <c r="N18" s="15">
-        <v>-80.965909090909</v>
+        <v>-80.758807588075</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,48 +1057,48 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>4</v>
+      </c>
+      <c r="D19" s="14">
         <v>11</v>
       </c>
-      <c r="D19" s="14">
-        <v>17</v>
-      </c>
       <c r="E19" s="15">
-        <v>-35.294117647058</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="F19" s="14">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G19" s="14">
         <v>41</v>
       </c>
       <c r="H19" s="15">
-        <v>-9.756097560975</v>
+        <v>-24.390243902439</v>
       </c>
       <c r="I19" s="14">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="J19" s="14">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="K19" s="15">
-        <v>0</v>
+        <v>-4.968944099378</v>
       </c>
       <c r="L19" s="15">
-        <v>13.636363636363</v>
+        <v>0.657894736842</v>
       </c>
       <c r="M19" s="15">
-        <v>-5.063291139240</v>
+        <v>-11.560693641618</v>
       </c>
       <c r="N19" s="15">
-        <v>-52.229299363057</v>
+        <v>-53.915662650602</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>1</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1107,31 +1107,31 @@
         <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G20" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H20" s="15">
-        <v>233.333333333333</v>
+        <v>700</v>
       </c>
       <c r="I20" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J20" s="14">
         <v>11</v>
       </c>
       <c r="K20" s="15">
-        <v>118.181818181818</v>
+        <v>127.272727272727</v>
       </c>
       <c r="L20" s="15">
-        <v>33.333333333333</v>
+        <v>25</v>
       </c>
       <c r="M20" s="15">
-        <v>118.181818181818</v>
+        <v>92.307692307692</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.233009708737</v>
+        <v>-92.283950617283</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D21" s="17">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E21" s="18">
-        <v>-43.333333333333</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="F21" s="17">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="G21" s="17">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H21" s="18">
-        <v>-8.536585365853</v>
+        <v>-11.688311688311</v>
       </c>
       <c r="I21" s="17">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="J21" s="17">
-        <v>325</v>
+        <v>344</v>
       </c>
       <c r="K21" s="18">
-        <v>0.307692307692</v>
+        <v>-1.744186046511</v>
       </c>
       <c r="L21" s="18">
-        <v>12.027491408934</v>
+        <v>5.295950155763</v>
       </c>
       <c r="M21" s="18">
-        <v>3.164556962025</v>
+        <v>-0.879765395894</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.204379562043</v>
+        <v>-76.657458563535</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,7 +1183,7 @@
         <v>20</v>
       </c>
       <c r="D22" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E22" s="15">
         <v>-100</v>
@@ -1192,7 +1192,7 @@
         <v>20</v>
       </c>
       <c r="G22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H22" s="15">
         <v>-100</v>
@@ -1201,10 +1201,10 @@
         <v>8</v>
       </c>
       <c r="J22" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K22" s="15">
-        <v>-46.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="L22" s="15">
         <v>-27.272727272727</v>
@@ -1221,13 +1221,13 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D23" s="14">
         <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F23" s="14">
         <v>9</v>
@@ -1239,19 +1239,19 @@
         <v>28.571428571428</v>
       </c>
       <c r="I23" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J23" s="14">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K23" s="15">
-        <v>-48.888888888888</v>
+        <v>-45.652173913043</v>
       </c>
       <c r="L23" s="15">
-        <v>-11.538461538461</v>
+        <v>-10.714285714285</v>
       </c>
       <c r="M23" s="15">
-        <v>-28.125</v>
+        <v>-26.470588235294</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D24" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E24" s="15">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F24" s="14">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G24" s="14">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="H24" s="15">
-        <v>12.686567164179</v>
+        <v>16.40625</v>
       </c>
       <c r="I24" s="14">
-        <v>491</v>
+        <v>531</v>
       </c>
       <c r="J24" s="14">
-        <v>569</v>
+        <v>601</v>
       </c>
       <c r="K24" s="15">
-        <v>-13.708260105448</v>
+        <v>-11.647254575707</v>
       </c>
       <c r="L24" s="15">
-        <v>24.936386768447</v>
+        <v>32.089552238806</v>
       </c>
       <c r="M24" s="15">
-        <v>61.513157894736</v>
+        <v>66.457680250783</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D25" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E25" s="15">
-        <v>21.052631578947</v>
+        <v>35</v>
       </c>
       <c r="F25" s="14">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G25" s="14">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="H25" s="15">
-        <v>3.157894736842</v>
+        <v>21.176470588235</v>
       </c>
       <c r="I25" s="14">
-        <v>268</v>
+        <v>296</v>
       </c>
       <c r="J25" s="14">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="K25" s="15">
-        <v>-32.493702770780</v>
+        <v>-29.016786570743</v>
       </c>
       <c r="L25" s="15">
-        <v>6.772908366533</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D26" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>83.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="F26" s="14">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G26" s="14">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H26" s="15">
-        <v>-3.846153846153</v>
+        <v>36.363636363636</v>
       </c>
       <c r="I26" s="14">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="J26" s="14">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="K26" s="15">
-        <v>14.893617021276</v>
+        <v>11.764705882352</v>
       </c>
       <c r="L26" s="15">
-        <v>30.120481927710</v>
+        <v>34.117647058823</v>
       </c>
       <c r="M26" s="15">
-        <v>22.727272727272</v>
+        <v>22.580645161290</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,11 +1387,11 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>1</v>
@@ -1406,13 +1406,13 @@
         <v>4</v>
       </c>
       <c r="J27" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K27" s="15">
-        <v>-50</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="L27" s="15">
-        <v>-42.857142857142</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F28" s="14">
         <v>8</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>166.666666666667</v>
+        <v>100</v>
       </c>
       <c r="I28" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J28" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K28" s="15">
-        <v>10</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L28" s="15">
-        <v>69.230769230769</v>
+        <v>84.615384615384</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1507,8 +1507,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1558,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1567,16 +1567,16 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J31" s="14">
         <v>4</v>
       </c>
       <c r="K31" s="15">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="L31" s="15">
-        <v>-36.363636363636</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-024pct.xlsx
+++ b/data/source/weekly/cs-en-us-024pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -860,14 +860,14 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="14">
-        <v>1</v>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G14" s="14">
         <v>1</v>
       </c>
       <c r="H14" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="14">
         <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
         <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J15" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K15" s="15">
-        <v>-55.555555555555</v>
+        <v>-50</v>
       </c>
       <c r="L15" s="15">
-        <v>-33.333333333333</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M15" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N15" s="15">
-        <v>-60</v>
+        <v>-58.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>1</v>
+      </c>
+      <c r="D16" s="14">
         <v>2</v>
       </c>
-      <c r="D16" s="14">
-        <v>1</v>
-      </c>
       <c r="E16" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
         <v>4</v>
       </c>
       <c r="G16" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H16" s="15">
-        <v>-20</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I16" s="14">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J16" s="14">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K16" s="15">
-        <v>-8.571428571428</v>
+        <v>-10.810810810810</v>
       </c>
       <c r="L16" s="15">
-        <v>-40.740740740740</v>
+        <v>-41.071428571428</v>
       </c>
       <c r="M16" s="15">
-        <v>-56.164383561643</v>
+        <v>-56</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.278388278388</v>
+        <v>-89.072847682119</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>-33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="F17" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G17" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H17" s="15">
-        <v>-7.692307692307</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="I17" s="14">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J17" s="14">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K17" s="15">
-        <v>-13.333333333333</v>
+        <v>-12.5</v>
       </c>
       <c r="L17" s="15">
-        <v>15.555555555555</v>
+        <v>24.444444444444</v>
       </c>
       <c r="M17" s="15">
-        <v>44.444444444444</v>
+        <v>40</v>
       </c>
       <c r="N17" s="15">
-        <v>-60.606060606060</v>
+        <v>-61.111111111111</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>7</v>
+      </c>
+      <c r="D18" s="14">
         <v>4</v>
       </c>
-      <c r="D18" s="14">
-        <v>3</v>
-      </c>
       <c r="E18" s="15">
-        <v>33.333333333333</v>
+        <v>75</v>
       </c>
       <c r="F18" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G18" s="14">
         <v>15</v>
       </c>
       <c r="H18" s="15">
-        <v>-26.666666666666</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="I18" s="14">
+        <v>77</v>
+      </c>
+      <c r="J18" s="14">
         <v>71</v>
       </c>
-      <c r="J18" s="14">
-        <v>67</v>
-      </c>
       <c r="K18" s="15">
-        <v>5.970149253731</v>
+        <v>8.450704225352</v>
       </c>
       <c r="L18" s="15">
-        <v>61.363636363636</v>
+        <v>75</v>
       </c>
       <c r="M18" s="15">
-        <v>69.047619047619</v>
+        <v>75</v>
       </c>
       <c r="N18" s="15">
-        <v>-80.758807588075</v>
+        <v>-80.357142857142</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E19" s="15">
-        <v>-63.636363636363</v>
+        <v>-20</v>
       </c>
       <c r="F19" s="14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G19" s="14">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="H19" s="15">
-        <v>-24.390243902439</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I19" s="14">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="J19" s="14">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="K19" s="15">
-        <v>-4.968944099378</v>
+        <v>-6.25</v>
       </c>
       <c r="L19" s="15">
-        <v>0.657894736842</v>
+        <v>2.484472049689</v>
       </c>
       <c r="M19" s="15">
-        <v>-11.560693641618</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="N19" s="15">
-        <v>-53.915662650602</v>
+        <v>-52.312138728323</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,11 +1100,11 @@
       <c r="C20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>0</v>
       </c>
       <c r="F20" s="14">
         <v>8</v>
@@ -1116,22 +1116,22 @@
         <v>700</v>
       </c>
       <c r="I20" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J20" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K20" s="15">
-        <v>127.272727272727</v>
+        <v>116.666666666667</v>
       </c>
       <c r="L20" s="15">
-        <v>25</v>
+        <v>23.809523809523</v>
       </c>
       <c r="M20" s="15">
-        <v>92.307692307692</v>
+        <v>100</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.283950617283</v>
+        <v>-92.330383480826</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D21" s="17">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E21" s="18">
-        <v>-31.578947368421</v>
+        <v>-7.407407407407</v>
       </c>
       <c r="F21" s="17">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G21" s="17">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H21" s="18">
-        <v>-11.688311688311</v>
+        <v>-17.045454545454</v>
       </c>
       <c r="I21" s="17">
-        <v>338</v>
+        <v>363</v>
       </c>
       <c r="J21" s="17">
-        <v>344</v>
+        <v>371</v>
       </c>
       <c r="K21" s="18">
-        <v>-1.744186046511</v>
+        <v>-2.156334231805</v>
       </c>
       <c r="L21" s="18">
-        <v>5.295950155763</v>
+        <v>9.009009009009</v>
       </c>
       <c r="M21" s="18">
-        <v>-0.879765395894</v>
+        <v>1.966292134831</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.657458563535</v>
+        <v>-76.474400518470</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1201,13 +1201,13 @@
         <v>8</v>
       </c>
       <c r="J22" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K22" s="15">
-        <v>-50</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="L22" s="15">
-        <v>-27.272727272727</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M22" s="15">
         <v>-27.272727272727</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E23" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
         <v>9</v>
       </c>
       <c r="G23" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H23" s="15">
-        <v>28.571428571428</v>
+        <v>12.5</v>
       </c>
       <c r="I23" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J23" s="14">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K23" s="15">
-        <v>-45.652173913043</v>
+        <v>-44.897959183673</v>
       </c>
       <c r="L23" s="15">
-        <v>-10.714285714285</v>
+        <v>-10</v>
       </c>
       <c r="M23" s="15">
-        <v>-26.470588235294</v>
+        <v>-20.588235294117</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D24" s="14">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E24" s="15">
         <v>25</v>
       </c>
       <c r="F24" s="14">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="G24" s="14">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="H24" s="15">
-        <v>16.40625</v>
+        <v>22.413793103448</v>
       </c>
       <c r="I24" s="14">
-        <v>531</v>
+        <v>562</v>
       </c>
       <c r="J24" s="14">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="K24" s="15">
-        <v>-11.647254575707</v>
+        <v>-10.08</v>
       </c>
       <c r="L24" s="15">
-        <v>32.089552238806</v>
+        <v>35.421686746988</v>
       </c>
       <c r="M24" s="15">
-        <v>66.457680250783</v>
+        <v>67.761194029850</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D25" s="14">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E25" s="15">
-        <v>35</v>
+        <v>5.882352941176</v>
       </c>
       <c r="F25" s="14">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="G25" s="14">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="H25" s="15">
-        <v>21.176470588235</v>
+        <v>21.333333333333</v>
       </c>
       <c r="I25" s="14">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="J25" s="14">
-        <v>417</v>
+        <v>434</v>
       </c>
       <c r="K25" s="15">
-        <v>-29.016786570743</v>
+        <v>-27.649769585253</v>
       </c>
       <c r="L25" s="15">
-        <v>14.285714285714</v>
+        <v>15.867158671586</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>6</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E26" s="15">
-        <v>-25</v>
+        <v>20</v>
       </c>
       <c r="F26" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G26" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H26" s="15">
-        <v>36.363636363636</v>
+        <v>28</v>
       </c>
       <c r="I26" s="14">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="J26" s="14">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="K26" s="15">
-        <v>11.764705882352</v>
+        <v>13.084112149532</v>
       </c>
       <c r="L26" s="15">
-        <v>34.117647058823</v>
+        <v>31.521739130434</v>
       </c>
       <c r="M26" s="15">
-        <v>22.580645161290</v>
+        <v>23.469387755102</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="14">
         <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
         <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J27" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K27" s="15">
-        <v>-55.555555555555</v>
+        <v>-50</v>
       </c>
       <c r="L27" s="15">
-        <v>-55.555555555555</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I28" s="14">
+        <v>27</v>
+      </c>
+      <c r="J28" s="14">
         <v>24</v>
       </c>
-      <c r="J28" s="14">
-        <v>21</v>
-      </c>
       <c r="K28" s="15">
-        <v>14.285714285714</v>
+        <v>12.5</v>
       </c>
       <c r="L28" s="15">
-        <v>84.615384615384</v>
+        <v>92.857142857142</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,29 +1469,29 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
-        <v>2</v>
-      </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>0</v>
       </c>
       <c r="I29" s="14">
         <v>3</v>
       </c>
       <c r="J29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K29" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>21</v>
       </c>
       <c r="N29" s="15">
-        <v>-76.923076923076</v>
+        <v>-81.25</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,29 +1510,29 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
-        <v>2</v>
-      </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>0</v>
       </c>
       <c r="I30" s="14">
         <v>3</v>
       </c>
       <c r="J30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>21</v>
@@ -1541,7 +1541,7 @@
         <v>21</v>
       </c>
       <c r="N30" s="15">
-        <v>-76.923076923076</v>
+        <v>-81.25</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1558,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
